--- a/ECG/Nurse_SBS_Scores/Patient5/Patient5_SBS_Scores.xlsx
+++ b/ECG/Nurse_SBS_Scores/Patient5/Patient5_SBS_Scores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b14a0d7b62cf6ad0/Sid Stuff/PROJECTS/iMEDS Design Team/Data Analysis/PedAccel/data_analysis/PythonPipeline/PatientData/Patient5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b14a0d7b62cf6ad0/Sid Stuff/PROJECTS/iMEDS Design Team/Data Analysis/PedAccel/ECG/Nurse_SBS_Scores/Patient5/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="9" documentId="11_369544B1DD7A53F15DB972D3525ED87656CCCC7F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F36563A-9E4F-44DC-BA37-9AA132C528B0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46470" yWindow="1470" windowWidth="21600" windowHeight="11055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -2241,10 +2241,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2556,10 +2555,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>717</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -2574,7 +2573,7 @@
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>0</v>
       </c>
     </row>
@@ -2586,7 +2585,7 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>1</v>
       </c>
     </row>
@@ -2598,7 +2597,7 @@
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -2610,7 +2609,7 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>1</v>
       </c>
     </row>
@@ -2622,7 +2621,7 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>2</v>
       </c>
     </row>
@@ -2634,7 +2633,7 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7">
         <v>0</v>
       </c>
     </row>
@@ -2646,7 +2645,7 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
         <v>0</v>
       </c>
     </row>
@@ -2658,7 +2657,7 @@
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9">
         <v>0</v>
       </c>
     </row>
@@ -2670,7 +2669,7 @@
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
         <v>0</v>
       </c>
     </row>
@@ -2682,7 +2681,7 @@
       <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
         <v>-2</v>
       </c>
     </row>
@@ -2694,7 +2693,7 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
         <v>-3</v>
       </c>
     </row>
@@ -2706,7 +2705,7 @@
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
         <v>-2</v>
       </c>
     </row>
@@ -2718,7 +2717,7 @@
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14">
         <v>-3</v>
       </c>
     </row>
@@ -2730,7 +2729,7 @@
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15">
         <v>-3</v>
       </c>
     </row>
@@ -2742,7 +2741,7 @@
       <c r="B16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16">
         <v>-2</v>
       </c>
     </row>
@@ -2754,7 +2753,7 @@
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>1</v>
       </c>
     </row>
@@ -2766,7 +2765,7 @@
       <c r="B18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18">
         <v>-1</v>
       </c>
     </row>
@@ -2778,7 +2777,7 @@
       <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19">
         <v>-2</v>
       </c>
     </row>
@@ -2790,7 +2789,7 @@
       <c r="B20" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20">
         <v>-2</v>
       </c>
     </row>
@@ -2802,7 +2801,7 @@
       <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21">
         <v>0</v>
       </c>
     </row>
@@ -2814,7 +2813,7 @@
       <c r="B22" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22">
         <v>0</v>
       </c>
     </row>
@@ -2826,7 +2825,7 @@
       <c r="B23" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23">
         <v>-2</v>
       </c>
     </row>
@@ -2838,7 +2837,7 @@
       <c r="B24" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24">
         <v>-1</v>
       </c>
     </row>
@@ -2850,7 +2849,7 @@
       <c r="B25" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25">
         <v>-1</v>
       </c>
     </row>
@@ -2862,7 +2861,7 @@
       <c r="B26" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26">
         <v>0</v>
       </c>
     </row>
@@ -2874,7 +2873,7 @@
       <c r="B27" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27">
         <v>-1</v>
       </c>
     </row>
@@ -2886,7 +2885,7 @@
       <c r="B28" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28">
         <v>-1</v>
       </c>
     </row>
@@ -2898,7 +2897,7 @@
       <c r="B29" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29">
         <v>-2</v>
       </c>
     </row>
@@ -2910,7 +2909,7 @@
       <c r="B30" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30">
         <v>0</v>
       </c>
     </row>
@@ -2922,7 +2921,7 @@
       <c r="B31" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31">
         <v>0</v>
       </c>
     </row>
@@ -2934,7 +2933,7 @@
       <c r="B32" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32">
         <v>0</v>
       </c>
     </row>
@@ -2946,7 +2945,7 @@
       <c r="B33" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33">
         <v>0</v>
       </c>
     </row>
@@ -2958,7 +2957,7 @@
       <c r="B34" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34">
         <v>0</v>
       </c>
     </row>
@@ -2970,7 +2969,7 @@
       <c r="B35" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35">
         <v>-3</v>
       </c>
     </row>
@@ -2982,7 +2981,7 @@
       <c r="B36" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36">
         <v>-3</v>
       </c>
     </row>
@@ -2994,7 +2993,7 @@
       <c r="B37" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37">
         <v>-2</v>
       </c>
     </row>
@@ -3006,7 +3005,7 @@
       <c r="B38" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38">
         <v>-1</v>
       </c>
     </row>
@@ -3018,7 +3017,7 @@
       <c r="B39" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39">
         <v>1</v>
       </c>
     </row>
@@ -3030,7 +3029,7 @@
       <c r="B40" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40">
         <v>-1</v>
       </c>
     </row>
@@ -3042,7 +3041,7 @@
       <c r="B41" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41">
         <v>1</v>
       </c>
     </row>
@@ -3054,7 +3053,7 @@
       <c r="B42" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42">
         <v>1</v>
       </c>
     </row>
@@ -3066,7 +3065,7 @@
       <c r="B43" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43">
         <v>-1</v>
       </c>
     </row>
@@ -3078,7 +3077,7 @@
       <c r="B44" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44">
         <v>-1</v>
       </c>
     </row>
@@ -3090,7 +3089,7 @@
       <c r="B45" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45">
         <v>-1</v>
       </c>
     </row>
@@ -3102,7 +3101,7 @@
       <c r="B46" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46">
         <v>-1</v>
       </c>
     </row>
@@ -3114,7 +3113,7 @@
       <c r="B47" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47">
         <v>-2</v>
       </c>
     </row>
@@ -3126,7 +3125,7 @@
       <c r="B48" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48">
         <v>2</v>
       </c>
     </row>
@@ -3138,7 +3137,7 @@
       <c r="B49" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49">
         <v>-2</v>
       </c>
     </row>
@@ -3150,7 +3149,7 @@
       <c r="B50" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50">
         <v>2</v>
       </c>
     </row>
@@ -3162,7 +3161,7 @@
       <c r="B51" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51">
         <v>-2</v>
       </c>
     </row>
@@ -3174,7 +3173,7 @@
       <c r="B52" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52">
         <v>-2</v>
       </c>
     </row>
@@ -3186,7 +3185,7 @@
       <c r="B53" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53">
         <v>-2</v>
       </c>
     </row>
@@ -3198,7 +3197,7 @@
       <c r="B54" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54">
         <v>-2</v>
       </c>
     </row>
@@ -3210,7 +3209,7 @@
       <c r="B55" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55">
         <v>-2</v>
       </c>
     </row>
@@ -3222,7 +3221,7 @@
       <c r="B56" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56">
         <v>-1</v>
       </c>
     </row>
@@ -3234,7 +3233,7 @@
       <c r="B57" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57">
         <v>-1</v>
       </c>
     </row>
@@ -3246,7 +3245,7 @@
       <c r="B58" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58">
         <v>-2</v>
       </c>
     </row>
@@ -3258,7 +3257,7 @@
       <c r="B59" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59">
         <v>-1</v>
       </c>
     </row>
@@ -3270,7 +3269,7 @@
       <c r="B60" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60">
         <v>-1</v>
       </c>
     </row>
@@ -3282,7 +3281,7 @@
       <c r="B61" t="s">
         <v>61</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61">
         <v>1</v>
       </c>
     </row>
@@ -3294,7 +3293,7 @@
       <c r="B62" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62">
         <v>-1</v>
       </c>
     </row>
@@ -3306,7 +3305,7 @@
       <c r="B63" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63">
         <v>1</v>
       </c>
     </row>
@@ -3318,7 +3317,7 @@
       <c r="B64" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64">
         <v>-1</v>
       </c>
     </row>
@@ -3330,7 +3329,7 @@
       <c r="B65" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="2">
+      <c r="C65">
         <v>-1</v>
       </c>
     </row>
@@ -3342,7 +3341,7 @@
       <c r="B66" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="2">
+      <c r="C66">
         <v>1</v>
       </c>
     </row>
@@ -3354,7 +3353,7 @@
       <c r="B67" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67">
         <v>-2</v>
       </c>
     </row>
@@ -3366,7 +3365,7 @@
       <c r="B68" t="s">
         <v>68</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68">
         <v>-2</v>
       </c>
     </row>
@@ -3378,7 +3377,7 @@
       <c r="B69" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69">
         <v>1</v>
       </c>
     </row>
@@ -3390,7 +3389,7 @@
       <c r="B70" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70">
         <v>-2</v>
       </c>
     </row>
@@ -3402,7 +3401,7 @@
       <c r="B71" t="s">
         <v>71</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71">
         <v>1</v>
       </c>
     </row>
@@ -3414,7 +3413,7 @@
       <c r="B72" t="s">
         <v>72</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72">
         <v>2</v>
       </c>
     </row>
@@ -3426,7 +3425,7 @@
       <c r="B73" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73">
         <v>-2</v>
       </c>
     </row>
@@ -3438,7 +3437,7 @@
       <c r="B74" t="s">
         <v>74</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74">
         <v>-2</v>
       </c>
     </row>
@@ -3450,7 +3449,7 @@
       <c r="B75" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75">
         <v>-1</v>
       </c>
     </row>
@@ -3462,7 +3461,7 @@
       <c r="B76" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76">
         <v>-2</v>
       </c>
     </row>
@@ -3474,7 +3473,7 @@
       <c r="B77" t="s">
         <v>77</v>
       </c>
-      <c r="C77" s="2">
+      <c r="C77">
         <v>0</v>
       </c>
     </row>
@@ -3486,7 +3485,7 @@
       <c r="B78" t="s">
         <v>78</v>
       </c>
-      <c r="C78" s="2">
+      <c r="C78">
         <v>-2</v>
       </c>
     </row>
@@ -3498,7 +3497,7 @@
       <c r="B79" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="2">
+      <c r="C79">
         <v>-2</v>
       </c>
     </row>
@@ -3510,7 +3509,7 @@
       <c r="B80" t="s">
         <v>80</v>
       </c>
-      <c r="C80" s="2">
+      <c r="C80">
         <v>0</v>
       </c>
     </row>
@@ -3522,7 +3521,7 @@
       <c r="B81" t="s">
         <v>81</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81">
         <v>-2</v>
       </c>
     </row>
@@ -3534,7 +3533,7 @@
       <c r="B82" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82">
         <v>0</v>
       </c>
     </row>
@@ -3546,7 +3545,7 @@
       <c r="B83" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83">
         <v>-2</v>
       </c>
     </row>
@@ -3558,7 +3557,7 @@
       <c r="B84" t="s">
         <v>84</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84">
         <v>0</v>
       </c>
     </row>
@@ -3570,7 +3569,7 @@
       <c r="B85" t="s">
         <v>85</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85">
         <v>1</v>
       </c>
     </row>
@@ -3582,7 +3581,7 @@
       <c r="B86" t="s">
         <v>86</v>
       </c>
-      <c r="C86" s="2">
+      <c r="C86">
         <v>1</v>
       </c>
     </row>
@@ -3594,7 +3593,7 @@
       <c r="B87" t="s">
         <v>87</v>
       </c>
-      <c r="C87" s="2">
+      <c r="C87">
         <v>-1</v>
       </c>
     </row>
@@ -3606,7 +3605,7 @@
       <c r="B88" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="2">
+      <c r="C88">
         <v>1</v>
       </c>
     </row>
@@ -3618,7 +3617,7 @@
       <c r="B89" t="s">
         <v>89</v>
       </c>
-      <c r="C89" s="2">
+      <c r="C89">
         <v>0</v>
       </c>
     </row>
@@ -3630,7 +3629,7 @@
       <c r="B90" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90">
         <v>0</v>
       </c>
     </row>
@@ -3642,7 +3641,7 @@
       <c r="B91" t="s">
         <v>91</v>
       </c>
-      <c r="C91" s="2">
+      <c r="C91">
         <v>2</v>
       </c>
     </row>
@@ -3654,7 +3653,7 @@
       <c r="B92" t="s">
         <v>92</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92">
         <v>1</v>
       </c>
     </row>
@@ -3666,7 +3665,7 @@
       <c r="B93" t="s">
         <v>93</v>
       </c>
-      <c r="C93" s="2">
+      <c r="C93">
         <v>2</v>
       </c>
     </row>
@@ -3678,7 +3677,7 @@
       <c r="B94" t="s">
         <v>94</v>
       </c>
-      <c r="C94" s="2">
+      <c r="C94">
         <v>0</v>
       </c>
     </row>
@@ -3690,7 +3689,7 @@
       <c r="B95" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="2">
+      <c r="C95">
         <v>0</v>
       </c>
     </row>
@@ -3702,7 +3701,7 @@
       <c r="B96" t="s">
         <v>96</v>
       </c>
-      <c r="C96" s="2">
+      <c r="C96">
         <v>1</v>
       </c>
     </row>
@@ -3714,7 +3713,7 @@
       <c r="B97" t="s">
         <v>97</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97">
         <v>0</v>
       </c>
     </row>
@@ -3726,7 +3725,7 @@
       <c r="B98" t="s">
         <v>98</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98">
         <v>1</v>
       </c>
     </row>
@@ -3738,7 +3737,7 @@
       <c r="B99" t="s">
         <v>99</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C99">
         <v>1</v>
       </c>
     </row>
@@ -3750,7 +3749,7 @@
       <c r="B100" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C100">
         <v>1</v>
       </c>
     </row>
@@ -3762,7 +3761,7 @@
       <c r="B101" t="s">
         <v>101</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C101">
         <v>0</v>
       </c>
     </row>
@@ -3774,7 +3773,7 @@
       <c r="B102" t="s">
         <v>102</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C102">
         <v>1</v>
       </c>
     </row>
@@ -3786,7 +3785,7 @@
       <c r="B103" t="s">
         <v>103</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C103">
         <v>-1</v>
       </c>
     </row>
@@ -3798,7 +3797,7 @@
       <c r="B104" t="s">
         <v>104</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104">
         <v>-2</v>
       </c>
     </row>
@@ -3810,7 +3809,7 @@
       <c r="B105" t="s">
         <v>105</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C105">
         <v>0</v>
       </c>
     </row>
@@ -3822,7 +3821,7 @@
       <c r="B106" t="s">
         <v>106</v>
       </c>
-      <c r="C106" s="2">
+      <c r="C106">
         <v>-2</v>
       </c>
     </row>
@@ -3834,7 +3833,7 @@
       <c r="B107" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107">
         <v>0</v>
       </c>
     </row>
@@ -3846,7 +3845,7 @@
       <c r="B108" t="s">
         <v>108</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108">
         <v>0</v>
       </c>
     </row>
@@ -3858,7 +3857,7 @@
       <c r="B109" t="s">
         <v>109</v>
       </c>
-      <c r="C109" s="2">
+      <c r="C109">
         <v>-2</v>
       </c>
     </row>
@@ -3870,7 +3869,7 @@
       <c r="B110" t="s">
         <v>110</v>
       </c>
-      <c r="C110" s="2">
+      <c r="C110">
         <v>-2</v>
       </c>
     </row>
@@ -3882,7 +3881,7 @@
       <c r="B111" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C111">
         <v>0</v>
       </c>
     </row>
@@ -3894,7 +3893,7 @@
       <c r="B112" t="s">
         <v>112</v>
       </c>
-      <c r="C112" s="2">
+      <c r="C112">
         <v>-1</v>
       </c>
     </row>
@@ -3906,7 +3905,7 @@
       <c r="B113" t="s">
         <v>113</v>
       </c>
-      <c r="C113" s="2">
+      <c r="C113">
         <v>1</v>
       </c>
     </row>
@@ -3918,7 +3917,7 @@
       <c r="B114" t="s">
         <v>114</v>
       </c>
-      <c r="C114" s="2">
+      <c r="C114">
         <v>1</v>
       </c>
     </row>
@@ -3930,7 +3929,7 @@
       <c r="B115" t="s">
         <v>115</v>
       </c>
-      <c r="C115" s="2">
+      <c r="C115">
         <v>1</v>
       </c>
     </row>
@@ -3942,7 +3941,7 @@
       <c r="B116" t="s">
         <v>116</v>
       </c>
-      <c r="C116" s="2">
+      <c r="C116">
         <v>0</v>
       </c>
     </row>
@@ -3954,7 +3953,7 @@
       <c r="B117" t="s">
         <v>117</v>
       </c>
-      <c r="C117" s="2">
+      <c r="C117">
         <v>1</v>
       </c>
     </row>
@@ -3966,7 +3965,7 @@
       <c r="B118" t="s">
         <v>118</v>
       </c>
-      <c r="C118" s="2">
+      <c r="C118">
         <v>0</v>
       </c>
     </row>
@@ -3978,7 +3977,7 @@
       <c r="B119" t="s">
         <v>119</v>
       </c>
-      <c r="C119" s="2">
+      <c r="C119">
         <v>0</v>
       </c>
     </row>
@@ -3990,7 +3989,7 @@
       <c r="B120" t="s">
         <v>120</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120">
         <v>1</v>
       </c>
     </row>
@@ -4002,7 +4001,7 @@
       <c r="B121" t="s">
         <v>121</v>
       </c>
-      <c r="C121" s="2">
+      <c r="C121">
         <v>1</v>
       </c>
     </row>
@@ -4014,7 +4013,7 @@
       <c r="B122" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="2">
+      <c r="C122">
         <v>0</v>
       </c>
     </row>
@@ -4026,7 +4025,7 @@
       <c r="B123" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="2">
+      <c r="C123">
         <v>-1</v>
       </c>
     </row>
@@ -4038,7 +4037,7 @@
       <c r="B124" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="2">
+      <c r="C124">
         <v>0</v>
       </c>
     </row>
@@ -4050,7 +4049,7 @@
       <c r="B125" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125">
         <v>-2</v>
       </c>
     </row>
@@ -4062,7 +4061,7 @@
       <c r="B126" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="2">
+      <c r="C126">
         <v>0</v>
       </c>
     </row>
@@ -4074,7 +4073,7 @@
       <c r="B127" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127">
         <v>-2</v>
       </c>
     </row>
@@ -4086,7 +4085,7 @@
       <c r="B128" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="2">
+      <c r="C128">
         <v>0</v>
       </c>
     </row>
@@ -4098,7 +4097,7 @@
       <c r="B129" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="2">
+      <c r="C129">
         <v>-2</v>
       </c>
     </row>
@@ -4110,7 +4109,7 @@
       <c r="B130" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="2">
+      <c r="C130">
         <v>0</v>
       </c>
     </row>
@@ -4122,7 +4121,7 @@
       <c r="B131" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="2">
+      <c r="C131">
         <v>-2</v>
       </c>
     </row>
@@ -4134,7 +4133,7 @@
       <c r="B132" t="s">
         <v>131</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132">
         <v>0</v>
       </c>
     </row>
@@ -4146,7 +4145,7 @@
       <c r="B133" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="2">
+      <c r="C133">
         <v>-2</v>
       </c>
     </row>
@@ -4158,7 +4157,7 @@
       <c r="B134" t="s">
         <v>133</v>
       </c>
-      <c r="C134" s="2">
+      <c r="C134">
         <v>1</v>
       </c>
     </row>
@@ -4170,7 +4169,7 @@
       <c r="B135" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="2">
+      <c r="C135">
         <v>-1</v>
       </c>
     </row>
@@ -4182,7 +4181,7 @@
       <c r="B136" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136">
         <v>1</v>
       </c>
     </row>
@@ -4194,7 +4193,7 @@
       <c r="B137" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="2">
+      <c r="C137">
         <v>-1</v>
       </c>
     </row>
@@ -4206,7 +4205,7 @@
       <c r="B138" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="2">
+      <c r="C138">
         <v>1</v>
       </c>
     </row>
@@ -4218,7 +4217,7 @@
       <c r="B139" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="2">
+      <c r="C139">
         <v>1</v>
       </c>
     </row>
@@ -4230,7 +4229,7 @@
       <c r="B140" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="2">
+      <c r="C140">
         <v>2</v>
       </c>
     </row>
@@ -4242,7 +4241,7 @@
       <c r="B141" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="2">
+      <c r="C141">
         <v>0</v>
       </c>
     </row>
@@ -4254,7 +4253,7 @@
       <c r="B142" t="s">
         <v>141</v>
       </c>
-      <c r="C142" s="2">
+      <c r="C142">
         <v>1</v>
       </c>
     </row>
@@ -4266,7 +4265,7 @@
       <c r="B143" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143">
         <v>1</v>
       </c>
     </row>
@@ -4278,7 +4277,7 @@
       <c r="B144" t="s">
         <v>143</v>
       </c>
-      <c r="C144" s="2">
+      <c r="C144">
         <v>2</v>
       </c>
     </row>
@@ -4290,7 +4289,7 @@
       <c r="B145" t="s">
         <v>144</v>
       </c>
-      <c r="C145" s="2">
+      <c r="C145">
         <v>2</v>
       </c>
     </row>
@@ -4302,7 +4301,7 @@
       <c r="B146" t="s">
         <v>145</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146">
         <v>2</v>
       </c>
     </row>
@@ -4314,7 +4313,7 @@
       <c r="B147" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="2">
+      <c r="C147">
         <v>2</v>
       </c>
     </row>
@@ -4326,7 +4325,7 @@
       <c r="B148" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="2">
+      <c r="C148">
         <v>2</v>
       </c>
     </row>
@@ -4338,7 +4337,7 @@
       <c r="B149" t="s">
         <v>148</v>
       </c>
-      <c r="C149" s="2">
+      <c r="C149">
         <v>0</v>
       </c>
     </row>
@@ -4350,7 +4349,7 @@
       <c r="B150" t="s">
         <v>149</v>
       </c>
-      <c r="C150" s="2">
+      <c r="C150">
         <v>1</v>
       </c>
     </row>
@@ -4362,7 +4361,7 @@
       <c r="B151" t="s">
         <v>150</v>
       </c>
-      <c r="C151" s="2">
+      <c r="C151">
         <v>1</v>
       </c>
     </row>
@@ -4374,7 +4373,7 @@
       <c r="B152" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="2">
+      <c r="C152">
         <v>0</v>
       </c>
     </row>
@@ -4386,7 +4385,7 @@
       <c r="B153" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="2">
+      <c r="C153">
         <v>1</v>
       </c>
     </row>
@@ -4398,7 +4397,7 @@
       <c r="B154" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="2">
+      <c r="C154">
         <v>0</v>
       </c>
     </row>
@@ -4410,7 +4409,7 @@
       <c r="B155" t="s">
         <v>154</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C155">
         <v>1</v>
       </c>
     </row>
@@ -4422,7 +4421,7 @@
       <c r="B156" t="s">
         <v>155</v>
       </c>
-      <c r="C156" s="2">
+      <c r="C156">
         <v>1</v>
       </c>
     </row>
@@ -4434,7 +4433,7 @@
       <c r="B157" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="2">
+      <c r="C157">
         <v>-1</v>
       </c>
     </row>
@@ -4446,7 +4445,7 @@
       <c r="B158" t="s">
         <v>157</v>
       </c>
-      <c r="C158" s="2">
+      <c r="C158">
         <v>1</v>
       </c>
     </row>
@@ -4458,7 +4457,7 @@
       <c r="B159" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="2">
+      <c r="C159">
         <v>-1</v>
       </c>
     </row>
@@ -4470,7 +4469,7 @@
       <c r="B160" t="s">
         <v>159</v>
       </c>
-      <c r="C160" s="2">
+      <c r="C160">
         <v>1</v>
       </c>
     </row>
@@ -4482,7 +4481,7 @@
       <c r="B161" t="s">
         <v>160</v>
       </c>
-      <c r="C161" s="2">
+      <c r="C161">
         <v>1</v>
       </c>
     </row>
@@ -4494,7 +4493,7 @@
       <c r="B162" t="s">
         <v>161</v>
       </c>
-      <c r="C162" s="2">
+      <c r="C162">
         <v>-1</v>
       </c>
     </row>
@@ -4506,7 +4505,7 @@
       <c r="B163" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="2">
+      <c r="C163">
         <v>1</v>
       </c>
     </row>
@@ -4518,7 +4517,7 @@
       <c r="B164" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="2">
+      <c r="C164">
         <v>-2</v>
       </c>
     </row>
@@ -4530,7 +4529,7 @@
       <c r="B165" t="s">
         <v>164</v>
       </c>
-      <c r="C165" s="2">
+      <c r="C165">
         <v>1</v>
       </c>
     </row>
@@ -4542,7 +4541,7 @@
       <c r="B166" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="2">
+      <c r="C166">
         <v>1</v>
       </c>
     </row>
@@ -4554,7 +4553,7 @@
       <c r="B167" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="2">
+      <c r="C167">
         <v>-1</v>
       </c>
     </row>
@@ -4566,7 +4565,7 @@
       <c r="B168" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="2">
+      <c r="C168">
         <v>1</v>
       </c>
     </row>
@@ -4578,7 +4577,7 @@
       <c r="B169" t="s">
         <v>168</v>
       </c>
-      <c r="C169" s="2">
+      <c r="C169">
         <v>-1</v>
       </c>
     </row>
@@ -4590,7 +4589,7 @@
       <c r="B170" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="2">
+      <c r="C170">
         <v>-1</v>
       </c>
     </row>
@@ -4602,7 +4601,7 @@
       <c r="B171" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C171">
         <v>1</v>
       </c>
     </row>
@@ -4614,7 +4613,7 @@
       <c r="B172" t="s">
         <v>171</v>
       </c>
-      <c r="C172" s="2">
+      <c r="C172">
         <v>-1</v>
       </c>
     </row>
@@ -4626,7 +4625,7 @@
       <c r="B173" t="s">
         <v>172</v>
       </c>
-      <c r="C173" s="2">
+      <c r="C173">
         <v>1</v>
       </c>
     </row>
@@ -4638,7 +4637,7 @@
       <c r="B174" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C174">
         <v>1</v>
       </c>
     </row>
@@ -4650,7 +4649,7 @@
       <c r="B175" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="2">
+      <c r="C175">
         <v>1</v>
       </c>
     </row>
@@ -4662,7 +4661,7 @@
       <c r="B176" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="2">
+      <c r="C176">
         <v>1</v>
       </c>
     </row>
@@ -4674,7 +4673,7 @@
       <c r="B177" t="s">
         <v>176</v>
       </c>
-      <c r="C177" s="2">
+      <c r="C177">
         <v>-1</v>
       </c>
     </row>
@@ -4686,7 +4685,7 @@
       <c r="B178" t="s">
         <v>177</v>
       </c>
-      <c r="C178" s="2">
+      <c r="C178">
         <v>1</v>
       </c>
     </row>
@@ -4698,7 +4697,7 @@
       <c r="B179" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="2">
+      <c r="C179">
         <v>-1</v>
       </c>
     </row>
@@ -4710,7 +4709,7 @@
       <c r="B180" t="s">
         <v>179</v>
       </c>
-      <c r="C180" s="2">
+      <c r="C180">
         <v>0</v>
       </c>
     </row>
@@ -4722,7 +4721,7 @@
       <c r="B181" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="2">
+      <c r="C181">
         <v>1</v>
       </c>
     </row>
@@ -4734,7 +4733,7 @@
       <c r="B182" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="2">
+      <c r="C182">
         <v>-1</v>
       </c>
     </row>
@@ -4746,7 +4745,7 @@
       <c r="B183" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="2">
+      <c r="C183">
         <v>-2</v>
       </c>
     </row>
@@ -4758,7 +4757,7 @@
       <c r="B184" t="s">
         <v>183</v>
       </c>
-      <c r="C184" s="2">
+      <c r="C184">
         <v>-1</v>
       </c>
     </row>
@@ -4770,7 +4769,7 @@
       <c r="B185" t="s">
         <v>184</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185">
         <v>-2</v>
       </c>
     </row>
@@ -4782,7 +4781,7 @@
       <c r="B186" t="s">
         <v>185</v>
       </c>
-      <c r="C186" s="2">
+      <c r="C186">
         <v>-1</v>
       </c>
     </row>
@@ -4794,7 +4793,7 @@
       <c r="B187" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187">
         <v>-1</v>
       </c>
     </row>
@@ -4806,7 +4805,7 @@
       <c r="B188" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C188">
         <v>-1</v>
       </c>
     </row>
@@ -4818,7 +4817,7 @@
       <c r="B189" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C189">
         <v>-2</v>
       </c>
     </row>
@@ -4830,7 +4829,7 @@
       <c r="B190" t="s">
         <v>189</v>
       </c>
-      <c r="C190" s="2">
+      <c r="C190">
         <v>2</v>
       </c>
     </row>
@@ -4842,7 +4841,7 @@
       <c r="B191" t="s">
         <v>190</v>
       </c>
-      <c r="C191" s="2">
+      <c r="C191">
         <v>-2</v>
       </c>
     </row>
@@ -4854,7 +4853,7 @@
       <c r="B192" t="s">
         <v>191</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C192">
         <v>2</v>
       </c>
     </row>
@@ -4866,7 +4865,7 @@
       <c r="B193" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C193">
         <v>1</v>
       </c>
     </row>
@@ -4878,7 +4877,7 @@
       <c r="B194" t="s">
         <v>193</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C194">
         <v>1</v>
       </c>
     </row>
@@ -4890,7 +4889,7 @@
       <c r="B195" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C195">
         <v>-1</v>
       </c>
     </row>
@@ -4902,7 +4901,7 @@
       <c r="B196" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="2">
+      <c r="C196">
         <v>-2</v>
       </c>
     </row>
@@ -4914,7 +4913,7 @@
       <c r="B197" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="2">
+      <c r="C197">
         <v>-2</v>
       </c>
     </row>
@@ -4926,7 +4925,7 @@
       <c r="B198" t="s">
         <v>197</v>
       </c>
-      <c r="C198" s="2">
+      <c r="C198">
         <v>-2</v>
       </c>
     </row>
@@ -4938,7 +4937,7 @@
       <c r="B199" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="2">
+      <c r="C199">
         <v>1</v>
       </c>
     </row>
@@ -4950,7 +4949,7 @@
       <c r="B200" t="s">
         <v>199</v>
       </c>
-      <c r="C200" s="2">
+      <c r="C200">
         <v>1</v>
       </c>
     </row>
@@ -4962,7 +4961,7 @@
       <c r="B201" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="2">
+      <c r="C201">
         <v>0</v>
       </c>
     </row>
@@ -4974,7 +4973,7 @@
       <c r="B202" t="s">
         <v>201</v>
       </c>
-      <c r="C202" s="2">
+      <c r="C202">
         <v>1</v>
       </c>
     </row>
@@ -4986,7 +4985,7 @@
       <c r="B203" t="s">
         <v>202</v>
       </c>
-      <c r="C203" s="2">
+      <c r="C203">
         <v>1</v>
       </c>
     </row>
@@ -4998,7 +4997,7 @@
       <c r="B204" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="2">
+      <c r="C204">
         <v>0</v>
       </c>
     </row>
@@ -5010,7 +5009,7 @@
       <c r="B205" t="s">
         <v>204</v>
       </c>
-      <c r="C205" s="2">
+      <c r="C205">
         <v>-1</v>
       </c>
     </row>
@@ -5022,7 +5021,7 @@
       <c r="B206" t="s">
         <v>205</v>
       </c>
-      <c r="C206" s="2">
+      <c r="C206">
         <v>1</v>
       </c>
     </row>
@@ -5034,7 +5033,7 @@
       <c r="B207" t="s">
         <v>206</v>
       </c>
-      <c r="C207" s="2">
+      <c r="C207">
         <v>-1</v>
       </c>
     </row>
@@ -5046,7 +5045,7 @@
       <c r="B208" t="s">
         <v>207</v>
       </c>
-      <c r="C208" s="2">
+      <c r="C208">
         <v>1</v>
       </c>
     </row>
@@ -5058,7 +5057,7 @@
       <c r="B209" t="s">
         <v>208</v>
       </c>
-      <c r="C209" s="2">
+      <c r="C209">
         <v>1</v>
       </c>
     </row>
@@ -5070,7 +5069,7 @@
       <c r="B210" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="2">
+      <c r="C210">
         <v>-1</v>
       </c>
     </row>
@@ -5082,7 +5081,7 @@
       <c r="B211" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="2">
+      <c r="C211">
         <v>-1</v>
       </c>
     </row>
@@ -5094,7 +5093,7 @@
       <c r="B212" t="s">
         <v>211</v>
       </c>
-      <c r="C212" s="2">
+      <c r="C212">
         <v>0</v>
       </c>
     </row>
@@ -5106,7 +5105,7 @@
       <c r="B213" t="s">
         <v>212</v>
       </c>
-      <c r="C213" s="2">
+      <c r="C213">
         <v>1</v>
       </c>
     </row>
@@ -5118,7 +5117,7 @@
       <c r="B214" t="s">
         <v>213</v>
       </c>
-      <c r="C214" s="2">
+      <c r="C214">
         <v>2</v>
       </c>
     </row>
@@ -5130,7 +5129,7 @@
       <c r="B215" t="s">
         <v>214</v>
       </c>
-      <c r="C215" s="2">
+      <c r="C215">
         <v>-1</v>
       </c>
     </row>
@@ -5142,7 +5141,7 @@
       <c r="B216" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="2">
+      <c r="C216">
         <v>-2</v>
       </c>
     </row>
@@ -5154,7 +5153,7 @@
       <c r="B217" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="2">
+      <c r="C217">
         <v>-1</v>
       </c>
     </row>
@@ -5166,7 +5165,7 @@
       <c r="B218" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="2">
+      <c r="C218">
         <v>-1</v>
       </c>
     </row>
@@ -5178,7 +5177,7 @@
       <c r="B219" t="s">
         <v>218</v>
       </c>
-      <c r="C219" s="2">
+      <c r="C219">
         <v>-1</v>
       </c>
     </row>
@@ -5190,7 +5189,7 @@
       <c r="B220" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="2">
+      <c r="C220">
         <v>-1</v>
       </c>
     </row>
@@ -5202,7 +5201,7 @@
       <c r="B221" t="s">
         <v>220</v>
       </c>
-      <c r="C221" s="2">
+      <c r="C221">
         <v>-1</v>
       </c>
     </row>
@@ -5214,7 +5213,7 @@
       <c r="B222" t="s">
         <v>221</v>
       </c>
-      <c r="C222" s="2">
+      <c r="C222">
         <v>1</v>
       </c>
     </row>
@@ -5226,7 +5225,7 @@
       <c r="B223" t="s">
         <v>222</v>
       </c>
-      <c r="C223" s="2">
+      <c r="C223">
         <v>2</v>
       </c>
     </row>
@@ -5238,7 +5237,7 @@
       <c r="B224" t="s">
         <v>223</v>
       </c>
-      <c r="C224" s="2">
+      <c r="C224">
         <v>0</v>
       </c>
     </row>
@@ -5250,7 +5249,7 @@
       <c r="B225" t="s">
         <v>224</v>
       </c>
-      <c r="C225" s="2">
+      <c r="C225">
         <v>-1</v>
       </c>
     </row>
@@ -5262,7 +5261,7 @@
       <c r="B226" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="2">
+      <c r="C226">
         <v>-1</v>
       </c>
     </row>
@@ -5274,7 +5273,7 @@
       <c r="B227" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="2">
+      <c r="C227">
         <v>1</v>
       </c>
     </row>
@@ -5286,7 +5285,7 @@
       <c r="B228" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="2">
+      <c r="C228">
         <v>0</v>
       </c>
     </row>
@@ -5298,7 +5297,7 @@
       <c r="B229" t="s">
         <v>228</v>
       </c>
-      <c r="C229" s="2">
+      <c r="C229">
         <v>-1</v>
       </c>
     </row>
@@ -5310,7 +5309,7 @@
       <c r="B230" t="s">
         <v>229</v>
       </c>
-      <c r="C230" s="2">
+      <c r="C230">
         <v>1</v>
       </c>
     </row>
@@ -5322,7 +5321,7 @@
       <c r="B231" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="2">
+      <c r="C231">
         <v>1</v>
       </c>
     </row>
@@ -5334,7 +5333,7 @@
       <c r="B232" t="s">
         <v>231</v>
       </c>
-      <c r="C232" s="2">
+      <c r="C232">
         <v>1</v>
       </c>
     </row>
@@ -5346,7 +5345,7 @@
       <c r="B233" t="s">
         <v>232</v>
       </c>
-      <c r="C233" s="2">
+      <c r="C233">
         <v>1</v>
       </c>
     </row>
@@ -5358,7 +5357,7 @@
       <c r="B234" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="2">
+      <c r="C234">
         <v>1</v>
       </c>
     </row>
@@ -5370,7 +5369,7 @@
       <c r="B235" t="s">
         <v>234</v>
       </c>
-      <c r="C235" s="2">
+      <c r="C235">
         <v>0</v>
       </c>
     </row>
@@ -5382,7 +5381,7 @@
       <c r="B236" t="s">
         <v>235</v>
       </c>
-      <c r="C236" s="2">
+      <c r="C236">
         <v>1</v>
       </c>
     </row>
@@ -5394,7 +5393,7 @@
       <c r="B237" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="2">
+      <c r="C237">
         <v>1</v>
       </c>
     </row>
@@ -5406,7 +5405,7 @@
       <c r="B238" t="s">
         <v>237</v>
       </c>
-      <c r="C238" s="2">
+      <c r="C238">
         <v>1</v>
       </c>
     </row>
@@ -5418,7 +5417,7 @@
       <c r="B239" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="2">
+      <c r="C239">
         <v>-1</v>
       </c>
     </row>
@@ -5430,7 +5429,7 @@
       <c r="B240" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="2">
+      <c r="C240">
         <v>1</v>
       </c>
     </row>
@@ -5442,7 +5441,7 @@
       <c r="B241" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="2">
+      <c r="C241">
         <v>0</v>
       </c>
     </row>
@@ -5454,7 +5453,7 @@
       <c r="B242" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="2">
+      <c r="C242">
         <v>1</v>
       </c>
     </row>
@@ -5466,7 +5465,7 @@
       <c r="B243" t="s">
         <v>242</v>
       </c>
-      <c r="C243" s="2">
+      <c r="C243">
         <v>0</v>
       </c>
     </row>
@@ -5478,7 +5477,7 @@
       <c r="B244" t="s">
         <v>243</v>
       </c>
-      <c r="C244" s="2">
+      <c r="C244">
         <v>1</v>
       </c>
     </row>
@@ -5490,7 +5489,7 @@
       <c r="B245" t="s">
         <v>244</v>
       </c>
-      <c r="C245" s="2">
+      <c r="C245">
         <v>1</v>
       </c>
     </row>
@@ -5502,7 +5501,7 @@
       <c r="B246" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="2">
+      <c r="C246">
         <v>1</v>
       </c>
     </row>
@@ -5514,7 +5513,7 @@
       <c r="B247" t="s">
         <v>246</v>
       </c>
-      <c r="C247" s="2">
+      <c r="C247">
         <v>1</v>
       </c>
     </row>
@@ -5526,7 +5525,7 @@
       <c r="B248" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="2">
+      <c r="C248">
         <v>1</v>
       </c>
     </row>
@@ -5538,7 +5537,7 @@
       <c r="B249" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="2">
+      <c r="C249">
         <v>1</v>
       </c>
     </row>
@@ -5550,7 +5549,7 @@
       <c r="B250" t="s">
         <v>249</v>
       </c>
-      <c r="C250" s="2">
+      <c r="C250">
         <v>1</v>
       </c>
     </row>
@@ -5562,7 +5561,7 @@
       <c r="B251" t="s">
         <v>250</v>
       </c>
-      <c r="C251" s="2">
+      <c r="C251">
         <v>1</v>
       </c>
     </row>
@@ -5574,7 +5573,7 @@
       <c r="B252" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="2">
+      <c r="C252">
         <v>1</v>
       </c>
     </row>
@@ -5586,7 +5585,7 @@
       <c r="B253" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="2">
+      <c r="C253">
         <v>1</v>
       </c>
     </row>
@@ -5598,7 +5597,7 @@
       <c r="B254" t="s">
         <v>253</v>
       </c>
-      <c r="C254" s="2">
+      <c r="C254">
         <v>1</v>
       </c>
     </row>
@@ -5610,7 +5609,7 @@
       <c r="B255" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="2">
+      <c r="C255">
         <v>1</v>
       </c>
     </row>
@@ -5622,7 +5621,7 @@
       <c r="B256" t="s">
         <v>255</v>
       </c>
-      <c r="C256" s="2">
+      <c r="C256">
         <v>1</v>
       </c>
     </row>
@@ -5634,7 +5633,7 @@
       <c r="B257" t="s">
         <v>256</v>
       </c>
-      <c r="C257" s="2">
+      <c r="C257">
         <v>1</v>
       </c>
     </row>
@@ -5646,7 +5645,7 @@
       <c r="B258" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="2">
+      <c r="C258">
         <v>1</v>
       </c>
     </row>
@@ -5658,7 +5657,7 @@
       <c r="B259" t="s">
         <v>258</v>
       </c>
-      <c r="C259" s="2">
+      <c r="C259">
         <v>1</v>
       </c>
     </row>
@@ -5670,7 +5669,7 @@
       <c r="B260" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="2">
+      <c r="C260">
         <v>1</v>
       </c>
     </row>
@@ -5682,7 +5681,7 @@
       <c r="B261" t="s">
         <v>260</v>
       </c>
-      <c r="C261" s="2">
+      <c r="C261">
         <v>1</v>
       </c>
     </row>
@@ -5694,7 +5693,7 @@
       <c r="B262" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="2">
+      <c r="C262">
         <v>1</v>
       </c>
     </row>
@@ -5706,7 +5705,7 @@
       <c r="B263" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="2">
+      <c r="C263">
         <v>1</v>
       </c>
     </row>
@@ -5718,7 +5717,7 @@
       <c r="B264" t="s">
         <v>263</v>
       </c>
-      <c r="C264" s="2">
+      <c r="C264">
         <v>1</v>
       </c>
     </row>
@@ -5730,7 +5729,7 @@
       <c r="B265" t="s">
         <v>264</v>
       </c>
-      <c r="C265" s="2">
+      <c r="C265">
         <v>1</v>
       </c>
     </row>
@@ -5742,7 +5741,7 @@
       <c r="B266" t="s">
         <v>265</v>
       </c>
-      <c r="C266" s="2">
+      <c r="C266">
         <v>1</v>
       </c>
     </row>
@@ -5754,7 +5753,7 @@
       <c r="B267" t="s">
         <v>266</v>
       </c>
-      <c r="C267" s="2">
+      <c r="C267">
         <v>-1</v>
       </c>
     </row>
@@ -5766,7 +5765,7 @@
       <c r="B268" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="2">
+      <c r="C268">
         <v>-1</v>
       </c>
     </row>
@@ -5778,7 +5777,7 @@
       <c r="B269" t="s">
         <v>268</v>
       </c>
-      <c r="C269" s="2">
+      <c r="C269">
         <v>1</v>
       </c>
     </row>
@@ -5790,7 +5789,7 @@
       <c r="B270" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="2">
+      <c r="C270">
         <v>-1</v>
       </c>
     </row>
@@ -5802,7 +5801,7 @@
       <c r="B271" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="2">
+      <c r="C271">
         <v>-2</v>
       </c>
     </row>
@@ -5814,7 +5813,7 @@
       <c r="B272" t="s">
         <v>271</v>
       </c>
-      <c r="C272" s="2">
+      <c r="C272">
         <v>-2</v>
       </c>
     </row>
@@ -5826,7 +5825,7 @@
       <c r="B273" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="2">
+      <c r="C273">
         <v>-2</v>
       </c>
     </row>
@@ -5838,7 +5837,7 @@
       <c r="B274" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="2">
+      <c r="C274">
         <v>-1</v>
       </c>
     </row>
@@ -5850,7 +5849,7 @@
       <c r="B275" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="2">
+      <c r="C275">
         <v>0</v>
       </c>
     </row>
@@ -5862,7 +5861,7 @@
       <c r="B276" t="s">
         <v>275</v>
       </c>
-      <c r="C276" s="2">
+      <c r="C276">
         <v>1</v>
       </c>
     </row>
@@ -5874,7 +5873,7 @@
       <c r="B277" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="2">
+      <c r="C277">
         <v>1</v>
       </c>
     </row>
@@ -5886,7 +5885,7 @@
       <c r="B278" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="2">
+      <c r="C278">
         <v>1</v>
       </c>
     </row>
@@ -5898,7 +5897,7 @@
       <c r="B279" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="2">
+      <c r="C279">
         <v>-1</v>
       </c>
     </row>
@@ -5910,7 +5909,7 @@
       <c r="B280" t="s">
         <v>279</v>
       </c>
-      <c r="C280" s="2">
+      <c r="C280">
         <v>-1</v>
       </c>
     </row>
@@ -5922,7 +5921,7 @@
       <c r="B281" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="2">
+      <c r="C281">
         <v>1</v>
       </c>
     </row>
@@ -5934,7 +5933,7 @@
       <c r="B282" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="2">
+      <c r="C282">
         <v>0</v>
       </c>
     </row>
@@ -5946,7 +5945,7 @@
       <c r="B283" t="s">
         <v>282</v>
       </c>
-      <c r="C283" s="2">
+      <c r="C283">
         <v>-1</v>
       </c>
     </row>
@@ -5958,7 +5957,7 @@
       <c r="B284" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C284">
         <v>1</v>
       </c>
     </row>
@@ -5970,7 +5969,7 @@
       <c r="B285" t="s">
         <v>284</v>
       </c>
-      <c r="C285" s="2">
+      <c r="C285">
         <v>1</v>
       </c>
     </row>
@@ -5982,7 +5981,7 @@
       <c r="B286" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="2">
+      <c r="C286">
         <v>-1</v>
       </c>
     </row>
@@ -5994,7 +5993,7 @@
       <c r="B287" t="s">
         <v>286</v>
       </c>
-      <c r="C287" s="2">
+      <c r="C287">
         <v>1</v>
       </c>
     </row>
@@ -6006,7 +6005,7 @@
       <c r="B288" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="2">
+      <c r="C288">
         <v>1</v>
       </c>
     </row>
@@ -6018,7 +6017,7 @@
       <c r="B289" t="s">
         <v>288</v>
       </c>
-      <c r="C289" s="2">
+      <c r="C289">
         <v>-1</v>
       </c>
     </row>
@@ -6030,7 +6029,7 @@
       <c r="B290" t="s">
         <v>289</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C290">
         <v>-1</v>
       </c>
     </row>
@@ -6042,7 +6041,7 @@
       <c r="B291" t="s">
         <v>290</v>
       </c>
-      <c r="C291" s="2">
+      <c r="C291">
         <v>1</v>
       </c>
     </row>
@@ -6054,7 +6053,7 @@
       <c r="B292" t="s">
         <v>291</v>
       </c>
-      <c r="C292" s="2">
+      <c r="C292">
         <v>-1</v>
       </c>
     </row>
@@ -6066,7 +6065,7 @@
       <c r="B293" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="2">
+      <c r="C293">
         <v>1</v>
       </c>
     </row>
@@ -6078,7 +6077,7 @@
       <c r="B294" t="s">
         <v>293</v>
       </c>
-      <c r="C294" s="2">
+      <c r="C294">
         <v>0</v>
       </c>
     </row>
@@ -6090,7 +6089,7 @@
       <c r="B295" t="s">
         <v>294</v>
       </c>
-      <c r="C295" s="2">
+      <c r="C295">
         <v>-1</v>
       </c>
     </row>
@@ -6102,7 +6101,7 @@
       <c r="B296" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="2">
+      <c r="C296">
         <v>1</v>
       </c>
     </row>
@@ -6114,7 +6113,7 @@
       <c r="B297" t="s">
         <v>296</v>
       </c>
-      <c r="C297" s="2">
+      <c r="C297">
         <v>-1</v>
       </c>
     </row>
@@ -6126,7 +6125,7 @@
       <c r="B298" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="2">
+      <c r="C298">
         <v>-1</v>
       </c>
     </row>
@@ -6138,7 +6137,7 @@
       <c r="B299" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="2">
+      <c r="C299">
         <v>-1</v>
       </c>
     </row>
@@ -6150,7 +6149,7 @@
       <c r="B300" t="s">
         <v>299</v>
       </c>
-      <c r="C300" s="2">
+      <c r="C300">
         <v>1</v>
       </c>
     </row>
@@ -6162,7 +6161,7 @@
       <c r="B301" t="s">
         <v>300</v>
       </c>
-      <c r="C301" s="2">
+      <c r="C301">
         <v>1</v>
       </c>
     </row>
@@ -6174,7 +6173,7 @@
       <c r="B302" t="s">
         <v>301</v>
       </c>
-      <c r="C302" s="2">
+      <c r="C302">
         <v>0</v>
       </c>
     </row>
@@ -6186,7 +6185,7 @@
       <c r="B303" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="2">
+      <c r="C303">
         <v>1</v>
       </c>
     </row>
@@ -6198,7 +6197,7 @@
       <c r="B304" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="2">
+      <c r="C304">
         <v>-1</v>
       </c>
     </row>
@@ -6210,7 +6209,7 @@
       <c r="B305" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="2">
+      <c r="C305">
         <v>1</v>
       </c>
     </row>
@@ -6222,7 +6221,7 @@
       <c r="B306" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="2">
+      <c r="C306">
         <v>-1</v>
       </c>
     </row>
@@ -6234,7 +6233,7 @@
       <c r="B307" t="s">
         <v>306</v>
       </c>
-      <c r="C307" s="2">
+      <c r="C307">
         <v>-1</v>
       </c>
     </row>
@@ -6246,7 +6245,7 @@
       <c r="B308" t="s">
         <v>307</v>
       </c>
-      <c r="C308" s="2">
+      <c r="C308">
         <v>-1</v>
       </c>
     </row>
@@ -6258,7 +6257,7 @@
       <c r="B309" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="2">
+      <c r="C309">
         <v>1</v>
       </c>
     </row>
@@ -6270,7 +6269,7 @@
       <c r="B310" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="2">
+      <c r="C310">
         <v>-1</v>
       </c>
     </row>
@@ -6282,7 +6281,7 @@
       <c r="B311" t="s">
         <v>310</v>
       </c>
-      <c r="C311" s="2">
+      <c r="C311">
         <v>1</v>
       </c>
     </row>
@@ -6294,7 +6293,7 @@
       <c r="B312" t="s">
         <v>311</v>
       </c>
-      <c r="C312" s="2">
+      <c r="C312">
         <v>-1</v>
       </c>
     </row>
@@ -6306,7 +6305,7 @@
       <c r="B313" t="s">
         <v>312</v>
       </c>
-      <c r="C313" s="2">
+      <c r="C313">
         <v>-1</v>
       </c>
     </row>
@@ -6318,7 +6317,7 @@
       <c r="B314" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="2">
+      <c r="C314">
         <v>-1</v>
       </c>
     </row>
@@ -6330,7 +6329,7 @@
       <c r="B315" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="2">
+      <c r="C315">
         <v>1</v>
       </c>
     </row>
@@ -6342,7 +6341,7 @@
       <c r="B316" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="2">
+      <c r="C316">
         <v>1</v>
       </c>
     </row>
@@ -6354,7 +6353,7 @@
       <c r="B317" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="2">
+      <c r="C317">
         <v>1</v>
       </c>
     </row>
@@ -6366,7 +6365,7 @@
       <c r="B318" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="2">
+      <c r="C318">
         <v>-1</v>
       </c>
     </row>
@@ -6378,7 +6377,7 @@
       <c r="B319" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="2">
+      <c r="C319">
         <v>-1</v>
       </c>
     </row>
@@ -6390,7 +6389,7 @@
       <c r="B320" t="s">
         <v>319</v>
       </c>
-      <c r="C320" s="2">
+      <c r="C320">
         <v>2</v>
       </c>
     </row>
@@ -6402,7 +6401,7 @@
       <c r="B321" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="2">
+      <c r="C321">
         <v>-1</v>
       </c>
     </row>
@@ -6414,7 +6413,7 @@
       <c r="B322" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="2">
+      <c r="C322">
         <v>-1</v>
       </c>
     </row>
@@ -6426,7 +6425,7 @@
       <c r="B323" t="s">
         <v>322</v>
       </c>
-      <c r="C323" s="2">
+      <c r="C323">
         <v>2</v>
       </c>
     </row>
@@ -6438,7 +6437,7 @@
       <c r="B324" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="2">
+      <c r="C324">
         <v>-1</v>
       </c>
     </row>
@@ -6450,7 +6449,7 @@
       <c r="B325" t="s">
         <v>324</v>
       </c>
-      <c r="C325" s="2">
+      <c r="C325">
         <v>1</v>
       </c>
     </row>
@@ -6462,7 +6461,7 @@
       <c r="B326" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="2">
+      <c r="C326">
         <v>-1</v>
       </c>
     </row>
@@ -6474,7 +6473,7 @@
       <c r="B327" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="2">
+      <c r="C327">
         <v>1</v>
       </c>
     </row>
@@ -6486,7 +6485,7 @@
       <c r="B328" t="s">
         <v>327</v>
       </c>
-      <c r="C328" s="2">
+      <c r="C328">
         <v>1</v>
       </c>
     </row>
@@ -6498,7 +6497,7 @@
       <c r="B329" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="2">
+      <c r="C329">
         <v>0</v>
       </c>
     </row>
@@ -6510,7 +6509,7 @@
       <c r="B330" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="2">
+      <c r="C330">
         <v>1</v>
       </c>
     </row>
@@ -6522,7 +6521,7 @@
       <c r="B331" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="2">
+      <c r="C331">
         <v>1</v>
       </c>
     </row>
@@ -6534,7 +6533,7 @@
       <c r="B332" t="s">
         <v>331</v>
       </c>
-      <c r="C332" s="2">
+      <c r="C332">
         <v>1</v>
       </c>
     </row>
@@ -6546,7 +6545,7 @@
       <c r="B333" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="2">
+      <c r="C333">
         <v>-1</v>
       </c>
     </row>
@@ -6558,7 +6557,7 @@
       <c r="B334" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="2">
+      <c r="C334">
         <v>-1</v>
       </c>
     </row>
@@ -6570,7 +6569,7 @@
       <c r="B335" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="2">
+      <c r="C335">
         <v>1</v>
       </c>
     </row>
@@ -6582,7 +6581,7 @@
       <c r="B336" t="s">
         <v>335</v>
       </c>
-      <c r="C336" s="2">
+      <c r="C336">
         <v>0</v>
       </c>
     </row>
@@ -6594,7 +6593,7 @@
       <c r="B337" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="2">
+      <c r="C337">
         <v>1</v>
       </c>
     </row>
@@ -6606,7 +6605,7 @@
       <c r="B338" t="s">
         <v>337</v>
       </c>
-      <c r="C338" s="2">
+      <c r="C338">
         <v>-1</v>
       </c>
     </row>
@@ -6618,7 +6617,7 @@
       <c r="B339" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="2">
+      <c r="C339">
         <v>-1</v>
       </c>
     </row>
@@ -6630,7 +6629,7 @@
       <c r="B340" t="s">
         <v>339</v>
       </c>
-      <c r="C340" s="2">
+      <c r="C340">
         <v>-1</v>
       </c>
     </row>
@@ -6642,7 +6641,7 @@
       <c r="B341" t="s">
         <v>340</v>
       </c>
-      <c r="C341" s="2">
+      <c r="C341">
         <v>-1</v>
       </c>
     </row>
@@ -6654,7 +6653,7 @@
       <c r="B342" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="2">
+      <c r="C342">
         <v>-1</v>
       </c>
     </row>
@@ -6666,7 +6665,7 @@
       <c r="B343" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="2">
+      <c r="C343">
         <v>-1</v>
       </c>
     </row>
@@ -6678,7 +6677,7 @@
       <c r="B344" t="s">
         <v>343</v>
       </c>
-      <c r="C344" s="2">
+      <c r="C344">
         <v>-1</v>
       </c>
     </row>
@@ -6690,7 +6689,7 @@
       <c r="B345" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="2">
+      <c r="C345">
         <v>-1</v>
       </c>
     </row>
@@ -6702,7 +6701,7 @@
       <c r="B346" t="s">
         <v>345</v>
       </c>
-      <c r="C346" s="2">
+      <c r="C346">
         <v>-1</v>
       </c>
     </row>
@@ -6714,7 +6713,7 @@
       <c r="B347" t="s">
         <v>346</v>
       </c>
-      <c r="C347" s="2">
+      <c r="C347">
         <v>-1</v>
       </c>
     </row>
@@ -6726,7 +6725,7 @@
       <c r="B348" t="s">
         <v>347</v>
       </c>
-      <c r="C348" s="2">
+      <c r="C348">
         <v>1</v>
       </c>
     </row>
@@ -6738,7 +6737,7 @@
       <c r="B349" t="s">
         <v>348</v>
       </c>
-      <c r="C349" s="2">
+      <c r="C349">
         <v>0</v>
       </c>
     </row>
@@ -6750,7 +6749,7 @@
       <c r="B350" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="2">
+      <c r="C350">
         <v>2</v>
       </c>
     </row>
@@ -6762,7 +6761,7 @@
       <c r="B351" t="s">
         <v>350</v>
       </c>
-      <c r="C351" s="2">
+      <c r="C351">
         <v>2</v>
       </c>
     </row>
@@ -6774,7 +6773,7 @@
       <c r="B352" t="s">
         <v>351</v>
       </c>
-      <c r="C352" s="2">
+      <c r="C352">
         <v>2</v>
       </c>
     </row>
@@ -6786,7 +6785,7 @@
       <c r="B353" t="s">
         <v>352</v>
       </c>
-      <c r="C353" s="2">
+      <c r="C353">
         <v>-1</v>
       </c>
     </row>
@@ -6798,7 +6797,7 @@
       <c r="B354" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="2">
+      <c r="C354">
         <v>-1</v>
       </c>
     </row>
@@ -6810,7 +6809,7 @@
       <c r="B355" t="s">
         <v>354</v>
       </c>
-      <c r="C355" s="2">
+      <c r="C355">
         <v>-1</v>
       </c>
     </row>
@@ -6822,7 +6821,7 @@
       <c r="B356" t="s">
         <v>355</v>
       </c>
-      <c r="C356" s="2">
+      <c r="C356">
         <v>1</v>
       </c>
     </row>
@@ -6834,7 +6833,7 @@
       <c r="B357" t="s">
         <v>356</v>
       </c>
-      <c r="C357" s="2">
+      <c r="C357">
         <v>1</v>
       </c>
     </row>
@@ -6846,7 +6845,7 @@
       <c r="B358" t="s">
         <v>357</v>
       </c>
-      <c r="C358" s="2">
+      <c r="C358">
         <v>1</v>
       </c>
     </row>
@@ -6858,7 +6857,7 @@
       <c r="B359" t="s">
         <v>358</v>
       </c>
-      <c r="C359" s="2">
+      <c r="C359">
         <v>-1</v>
       </c>
     </row>
@@ -6870,7 +6869,7 @@
       <c r="B360" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="2">
+      <c r="C360">
         <v>1</v>
       </c>
     </row>
@@ -6882,7 +6881,7 @@
       <c r="B361" t="s">
         <v>360</v>
       </c>
-      <c r="C361" s="2">
+      <c r="C361">
         <v>1</v>
       </c>
     </row>
@@ -6894,7 +6893,7 @@
       <c r="B362" t="s">
         <v>361</v>
       </c>
-      <c r="C362" s="2">
+      <c r="C362">
         <v>-1</v>
       </c>
     </row>
@@ -6906,7 +6905,7 @@
       <c r="B363" t="s">
         <v>362</v>
       </c>
-      <c r="C363" s="2">
+      <c r="C363">
         <v>1</v>
       </c>
     </row>
@@ -6918,7 +6917,7 @@
       <c r="B364" t="s">
         <v>363</v>
       </c>
-      <c r="C364" s="2">
+      <c r="C364">
         <v>1</v>
       </c>
     </row>
@@ -6930,7 +6929,7 @@
       <c r="B365" t="s">
         <v>364</v>
       </c>
-      <c r="C365" s="2">
+      <c r="C365">
         <v>1</v>
       </c>
     </row>
@@ -6942,7 +6941,7 @@
       <c r="B366" t="s">
         <v>365</v>
       </c>
-      <c r="C366" s="2">
+      <c r="C366">
         <v>1</v>
       </c>
     </row>
@@ -6954,7 +6953,7 @@
       <c r="B367" t="s">
         <v>366</v>
       </c>
-      <c r="C367" s="2">
+      <c r="C367">
         <v>1</v>
       </c>
     </row>
@@ -6966,7 +6965,7 @@
       <c r="B368" t="s">
         <v>367</v>
       </c>
-      <c r="C368" s="2">
+      <c r="C368">
         <v>1</v>
       </c>
     </row>
@@ -6978,7 +6977,7 @@
       <c r="B369" t="s">
         <v>368</v>
       </c>
-      <c r="C369" s="2">
+      <c r="C369">
         <v>1</v>
       </c>
     </row>
@@ -6990,7 +6989,7 @@
       <c r="B370" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="2">
+      <c r="C370">
         <v>1</v>
       </c>
     </row>
@@ -7002,7 +7001,7 @@
       <c r="B371" t="s">
         <v>370</v>
       </c>
-      <c r="C371" s="2">
+      <c r="C371">
         <v>-1</v>
       </c>
     </row>
@@ -7014,7 +7013,7 @@
       <c r="B372" t="s">
         <v>371</v>
       </c>
-      <c r="C372" s="2">
+      <c r="C372">
         <v>1</v>
       </c>
     </row>
@@ -7026,7 +7025,7 @@
       <c r="B373" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="2">
+      <c r="C373">
         <v>1</v>
       </c>
     </row>
@@ -7038,7 +7037,7 @@
       <c r="B374" t="s">
         <v>373</v>
       </c>
-      <c r="C374" s="2">
+      <c r="C374">
         <v>1</v>
       </c>
     </row>
@@ -7050,7 +7049,7 @@
       <c r="B375" t="s">
         <v>374</v>
       </c>
-      <c r="C375" s="2">
+      <c r="C375">
         <v>1</v>
       </c>
     </row>
@@ -7062,7 +7061,7 @@
       <c r="B376" t="s">
         <v>375</v>
       </c>
-      <c r="C376" s="2">
+      <c r="C376">
         <v>1</v>
       </c>
     </row>
@@ -7074,7 +7073,7 @@
       <c r="B377" t="s">
         <v>376</v>
       </c>
-      <c r="C377" s="2">
+      <c r="C377">
         <v>-1</v>
       </c>
     </row>
@@ -7086,7 +7085,7 @@
       <c r="B378" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="2">
+      <c r="C378">
         <v>1</v>
       </c>
     </row>
@@ -7098,7 +7097,7 @@
       <c r="B379" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="2">
+      <c r="C379">
         <v>1</v>
       </c>
     </row>
@@ -7110,7 +7109,7 @@
       <c r="B380" t="s">
         <v>379</v>
       </c>
-      <c r="C380" s="2">
+      <c r="C380">
         <v>-1</v>
       </c>
     </row>
@@ -7122,7 +7121,7 @@
       <c r="B381" t="s">
         <v>380</v>
       </c>
-      <c r="C381" s="2">
+      <c r="C381">
         <v>1</v>
       </c>
     </row>
@@ -7134,7 +7133,7 @@
       <c r="B382" t="s">
         <v>381</v>
       </c>
-      <c r="C382" s="2">
+      <c r="C382">
         <v>-1</v>
       </c>
     </row>
@@ -7146,7 +7145,7 @@
       <c r="B383" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="2">
+      <c r="C383">
         <v>1</v>
       </c>
     </row>
@@ -7158,7 +7157,7 @@
       <c r="B384" t="s">
         <v>383</v>
       </c>
-      <c r="C384" s="2">
+      <c r="C384">
         <v>1</v>
       </c>
     </row>
@@ -7170,7 +7169,7 @@
       <c r="B385" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="2">
+      <c r="C385">
         <v>1</v>
       </c>
     </row>
@@ -7182,7 +7181,7 @@
       <c r="B386" t="s">
         <v>385</v>
       </c>
-      <c r="C386" s="2">
+      <c r="C386">
         <v>-1</v>
       </c>
     </row>
@@ -7194,7 +7193,7 @@
       <c r="B387" t="s">
         <v>386</v>
       </c>
-      <c r="C387" s="2">
+      <c r="C387">
         <v>1</v>
       </c>
     </row>
@@ -7206,7 +7205,7 @@
       <c r="B388" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="2">
+      <c r="C388">
         <v>1</v>
       </c>
     </row>
@@ -7218,7 +7217,7 @@
       <c r="B389" t="s">
         <v>388</v>
       </c>
-      <c r="C389" s="2">
+      <c r="C389">
         <v>1</v>
       </c>
     </row>
@@ -7230,7 +7229,7 @@
       <c r="B390" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="2">
+      <c r="C390">
         <v>-1</v>
       </c>
     </row>
@@ -7242,7 +7241,7 @@
       <c r="B391" t="s">
         <v>390</v>
       </c>
-      <c r="C391" s="2">
+      <c r="C391">
         <v>1</v>
       </c>
     </row>
@@ -7254,7 +7253,7 @@
       <c r="B392" t="s">
         <v>391</v>
       </c>
-      <c r="C392" s="2">
+      <c r="C392">
         <v>-1</v>
       </c>
     </row>
@@ -7266,7 +7265,7 @@
       <c r="B393" t="s">
         <v>392</v>
       </c>
-      <c r="C393" s="2">
+      <c r="C393">
         <v>1</v>
       </c>
     </row>
@@ -7278,7 +7277,7 @@
       <c r="B394" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="2">
+      <c r="C394">
         <v>-1</v>
       </c>
     </row>
@@ -7290,7 +7289,7 @@
       <c r="B395" t="s">
         <v>394</v>
       </c>
-      <c r="C395" s="2">
+      <c r="C395">
         <v>-1</v>
       </c>
     </row>
@@ -7302,7 +7301,7 @@
       <c r="B396" t="s">
         <v>395</v>
       </c>
-      <c r="C396" s="2">
+      <c r="C396">
         <v>-1</v>
       </c>
     </row>
@@ -7314,7 +7313,7 @@
       <c r="B397" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="2">
+      <c r="C397">
         <v>-1</v>
       </c>
     </row>
@@ -7326,7 +7325,7 @@
       <c r="B398" t="s">
         <v>396</v>
       </c>
-      <c r="C398" s="2">
+      <c r="C398">
         <v>0</v>
       </c>
     </row>
@@ -7338,7 +7337,7 @@
       <c r="B399" t="s">
         <v>397</v>
       </c>
-      <c r="C399" s="2">
+      <c r="C399">
         <v>-1</v>
       </c>
     </row>
@@ -7350,7 +7349,7 @@
       <c r="B400" t="s">
         <v>398</v>
       </c>
-      <c r="C400" s="2">
+      <c r="C400">
         <v>1</v>
       </c>
     </row>
@@ -7362,7 +7361,7 @@
       <c r="B401" t="s">
         <v>399</v>
       </c>
-      <c r="C401" s="2">
+      <c r="C401">
         <v>1</v>
       </c>
     </row>
@@ -7374,7 +7373,7 @@
       <c r="B402" t="s">
         <v>400</v>
       </c>
-      <c r="C402" s="2">
+      <c r="C402">
         <v>-1</v>
       </c>
     </row>
@@ -7386,7 +7385,7 @@
       <c r="B403" t="s">
         <v>401</v>
       </c>
-      <c r="C403" s="2">
+      <c r="C403">
         <v>-1</v>
       </c>
     </row>
@@ -7398,7 +7397,7 @@
       <c r="B404" t="s">
         <v>402</v>
       </c>
-      <c r="C404" s="2">
+      <c r="C404">
         <v>1</v>
       </c>
     </row>
@@ -7410,7 +7409,7 @@
       <c r="B405" t="s">
         <v>403</v>
       </c>
-      <c r="C405" s="2">
+      <c r="C405">
         <v>1</v>
       </c>
     </row>
@@ -7422,7 +7421,7 @@
       <c r="B406" t="s">
         <v>404</v>
       </c>
-      <c r="C406" s="2">
+      <c r="C406">
         <v>-1</v>
       </c>
     </row>
@@ -7434,7 +7433,7 @@
       <c r="B407" t="s">
         <v>405</v>
       </c>
-      <c r="C407" s="2">
+      <c r="C407">
         <v>1</v>
       </c>
     </row>
@@ -7446,7 +7445,7 @@
       <c r="B408" t="s">
         <v>406</v>
       </c>
-      <c r="C408" s="2">
+      <c r="C408">
         <v>-1</v>
       </c>
     </row>
@@ -7458,7 +7457,7 @@
       <c r="B409" t="s">
         <v>407</v>
       </c>
-      <c r="C409" s="2">
+      <c r="C409">
         <v>1</v>
       </c>
     </row>
@@ -7470,7 +7469,7 @@
       <c r="B410" t="s">
         <v>408</v>
       </c>
-      <c r="C410" s="2">
+      <c r="C410">
         <v>1</v>
       </c>
     </row>
@@ -7482,7 +7481,7 @@
       <c r="B411" t="s">
         <v>409</v>
       </c>
-      <c r="C411" s="2">
+      <c r="C411">
         <v>0</v>
       </c>
     </row>
@@ -7494,7 +7493,7 @@
       <c r="B412" t="s">
         <v>410</v>
       </c>
-      <c r="C412" s="2">
+      <c r="C412">
         <v>1</v>
       </c>
     </row>
@@ -7506,7 +7505,7 @@
       <c r="B413" t="s">
         <v>411</v>
       </c>
-      <c r="C413" s="2">
+      <c r="C413">
         <v>0</v>
       </c>
     </row>
@@ -7518,7 +7517,7 @@
       <c r="B414" t="s">
         <v>412</v>
       </c>
-      <c r="C414" s="2">
+      <c r="C414">
         <v>1</v>
       </c>
     </row>
@@ -7530,7 +7529,7 @@
       <c r="B415" t="s">
         <v>413</v>
       </c>
-      <c r="C415" s="2">
+      <c r="C415">
         <v>0</v>
       </c>
     </row>
@@ -7542,7 +7541,7 @@
       <c r="B416" t="s">
         <v>414</v>
       </c>
-      <c r="C416" s="2">
+      <c r="C416">
         <v>-2</v>
       </c>
     </row>
@@ -7554,7 +7553,7 @@
       <c r="B417" t="s">
         <v>415</v>
       </c>
-      <c r="C417" s="2">
+      <c r="C417">
         <v>-2</v>
       </c>
     </row>
@@ -7566,7 +7565,7 @@
       <c r="B418" t="s">
         <v>416</v>
       </c>
-      <c r="C418" s="2">
+      <c r="C418">
         <v>0</v>
       </c>
     </row>
@@ -7578,7 +7577,7 @@
       <c r="B419" t="s">
         <v>417</v>
       </c>
-      <c r="C419" s="2">
+      <c r="C419">
         <v>0</v>
       </c>
     </row>
@@ -7590,7 +7589,7 @@
       <c r="B420" t="s">
         <v>418</v>
       </c>
-      <c r="C420" s="2">
+      <c r="C420">
         <v>0</v>
       </c>
     </row>
@@ -7602,7 +7601,7 @@
       <c r="B421" t="s">
         <v>419</v>
       </c>
-      <c r="C421" s="2">
+      <c r="C421">
         <v>-2</v>
       </c>
     </row>
@@ -7614,7 +7613,7 @@
       <c r="B422" t="s">
         <v>420</v>
       </c>
-      <c r="C422" s="2">
+      <c r="C422">
         <v>-1</v>
       </c>
     </row>
@@ -7626,7 +7625,7 @@
       <c r="B423" t="s">
         <v>421</v>
       </c>
-      <c r="C423" s="2">
+      <c r="C423">
         <v>1</v>
       </c>
     </row>
@@ -7638,7 +7637,7 @@
       <c r="B424" t="s">
         <v>422</v>
       </c>
-      <c r="C424" s="2">
+      <c r="C424">
         <v>-1</v>
       </c>
     </row>
@@ -7650,7 +7649,7 @@
       <c r="B425" t="s">
         <v>423</v>
       </c>
-      <c r="C425" s="2">
+      <c r="C425">
         <v>1</v>
       </c>
     </row>
@@ -7662,7 +7661,7 @@
       <c r="B426" t="s">
         <v>424</v>
       </c>
-      <c r="C426" s="2">
+      <c r="C426">
         <v>1</v>
       </c>
     </row>
@@ -7674,7 +7673,7 @@
       <c r="B427" t="s">
         <v>425</v>
       </c>
-      <c r="C427" s="2">
+      <c r="C427">
         <v>-1</v>
       </c>
     </row>
@@ -7686,7 +7685,7 @@
       <c r="B428" t="s">
         <v>426</v>
       </c>
-      <c r="C428" s="2">
+      <c r="C428">
         <v>-1</v>
       </c>
     </row>
@@ -7698,7 +7697,7 @@
       <c r="B429" t="s">
         <v>427</v>
       </c>
-      <c r="C429" s="2">
+      <c r="C429">
         <v>1</v>
       </c>
     </row>
@@ -7710,7 +7709,7 @@
       <c r="B430" t="s">
         <v>428</v>
       </c>
-      <c r="C430" s="2">
+      <c r="C430">
         <v>1</v>
       </c>
     </row>
@@ -7722,7 +7721,7 @@
       <c r="B431" t="s">
         <v>429</v>
       </c>
-      <c r="C431" s="2">
+      <c r="C431">
         <v>-1</v>
       </c>
     </row>
@@ -7734,7 +7733,7 @@
       <c r="B432" t="s">
         <v>430</v>
       </c>
-      <c r="C432" s="2">
+      <c r="C432">
         <v>-1</v>
       </c>
     </row>
@@ -7746,7 +7745,7 @@
       <c r="B433" t="s">
         <v>431</v>
       </c>
-      <c r="C433" s="2">
+      <c r="C433">
         <v>1</v>
       </c>
     </row>
@@ -7758,7 +7757,7 @@
       <c r="B434" t="s">
         <v>432</v>
       </c>
-      <c r="C434" s="2">
+      <c r="C434">
         <v>1</v>
       </c>
     </row>
@@ -7770,7 +7769,7 @@
       <c r="B435" t="s">
         <v>433</v>
       </c>
-      <c r="C435" s="2">
+      <c r="C435">
         <v>1</v>
       </c>
     </row>
@@ -7782,7 +7781,7 @@
       <c r="B436" t="s">
         <v>434</v>
       </c>
-      <c r="C436" s="2">
+      <c r="C436">
         <v>-1</v>
       </c>
     </row>
@@ -7794,7 +7793,7 @@
       <c r="B437" t="s">
         <v>435</v>
       </c>
-      <c r="C437" s="2">
+      <c r="C437">
         <v>0</v>
       </c>
     </row>
@@ -7806,7 +7805,7 @@
       <c r="B438" t="s">
         <v>436</v>
       </c>
-      <c r="C438" s="2">
+      <c r="C438">
         <v>2</v>
       </c>
     </row>
@@ -7818,7 +7817,7 @@
       <c r="B439" t="s">
         <v>437</v>
       </c>
-      <c r="C439" s="2">
+      <c r="C439">
         <v>2</v>
       </c>
     </row>
@@ -7830,7 +7829,7 @@
       <c r="B440" t="s">
         <v>438</v>
       </c>
-      <c r="C440" s="2">
+      <c r="C440">
         <v>1</v>
       </c>
     </row>
@@ -7842,7 +7841,7 @@
       <c r="B441" t="s">
         <v>439</v>
       </c>
-      <c r="C441" s="2">
+      <c r="C441">
         <v>2</v>
       </c>
     </row>
@@ -7854,7 +7853,7 @@
       <c r="B442" t="s">
         <v>440</v>
       </c>
-      <c r="C442" s="2">
+      <c r="C442">
         <v>1</v>
       </c>
     </row>
@@ -7866,7 +7865,7 @@
       <c r="B443" t="s">
         <v>441</v>
       </c>
-      <c r="C443" s="2">
+      <c r="C443">
         <v>0</v>
       </c>
     </row>
@@ -7878,7 +7877,7 @@
       <c r="B444" t="s">
         <v>442</v>
       </c>
-      <c r="C444" s="2">
+      <c r="C444">
         <v>0</v>
       </c>
     </row>
@@ -7890,7 +7889,7 @@
       <c r="B445" t="s">
         <v>443</v>
       </c>
-      <c r="C445" s="2">
+      <c r="C445">
         <v>1</v>
       </c>
     </row>
@@ -7902,7 +7901,7 @@
       <c r="B446" t="s">
         <v>444</v>
       </c>
-      <c r="C446" s="2">
+      <c r="C446">
         <v>-1</v>
       </c>
     </row>
@@ -7914,7 +7913,7 @@
       <c r="B447" t="s">
         <v>445</v>
       </c>
-      <c r="C447" s="2">
+      <c r="C447">
         <v>1</v>
       </c>
     </row>
@@ -7926,7 +7925,7 @@
       <c r="B448" t="s">
         <v>446</v>
       </c>
-      <c r="C448" s="2">
+      <c r="C448">
         <v>-1</v>
       </c>
     </row>
@@ -7938,7 +7937,7 @@
       <c r="B449" t="s">
         <v>447</v>
       </c>
-      <c r="C449" s="2">
+      <c r="C449">
         <v>-1</v>
       </c>
     </row>
@@ -7950,7 +7949,7 @@
       <c r="B450" t="s">
         <v>448</v>
       </c>
-      <c r="C450" s="2">
+      <c r="C450">
         <v>1</v>
       </c>
     </row>
@@ -7962,7 +7961,7 @@
       <c r="B451" t="s">
         <v>449</v>
       </c>
-      <c r="C451" s="2">
+      <c r="C451">
         <v>-1</v>
       </c>
     </row>
@@ -7974,7 +7973,7 @@
       <c r="B452" t="s">
         <v>450</v>
       </c>
-      <c r="C452" s="2">
+      <c r="C452">
         <v>-1</v>
       </c>
     </row>
@@ -7986,7 +7985,7 @@
       <c r="B453" t="s">
         <v>451</v>
       </c>
-      <c r="C453" s="2">
+      <c r="C453">
         <v>-1</v>
       </c>
     </row>
@@ -7998,7 +7997,7 @@
       <c r="B454" t="s">
         <v>452</v>
       </c>
-      <c r="C454" s="2">
+      <c r="C454">
         <v>-1</v>
       </c>
     </row>
@@ -8010,7 +8009,7 @@
       <c r="B455" t="s">
         <v>453</v>
       </c>
-      <c r="C455" s="2">
+      <c r="C455">
         <v>-2</v>
       </c>
     </row>
@@ -8022,7 +8021,7 @@
       <c r="B456" t="s">
         <v>454</v>
       </c>
-      <c r="C456" s="2">
+      <c r="C456">
         <v>1</v>
       </c>
     </row>
@@ -8034,7 +8033,7 @@
       <c r="B457" t="s">
         <v>455</v>
       </c>
-      <c r="C457" s="2">
+      <c r="C457">
         <v>-2</v>
       </c>
     </row>
@@ -8046,7 +8045,7 @@
       <c r="B458" t="s">
         <v>456</v>
       </c>
-      <c r="C458" s="2">
+      <c r="C458">
         <v>-1</v>
       </c>
     </row>
@@ -8058,7 +8057,7 @@
       <c r="B459" t="s">
         <v>457</v>
       </c>
-      <c r="C459" s="2">
+      <c r="C459">
         <v>-2</v>
       </c>
     </row>
@@ -8070,7 +8069,7 @@
       <c r="B460" t="s">
         <v>458</v>
       </c>
-      <c r="C460" s="2">
+      <c r="C460">
         <v>-1</v>
       </c>
     </row>
@@ -8082,7 +8081,7 @@
       <c r="B461" t="s">
         <v>459</v>
       </c>
-      <c r="C461" s="2">
+      <c r="C461">
         <v>-1</v>
       </c>
     </row>
@@ -8094,7 +8093,7 @@
       <c r="B462" t="s">
         <v>460</v>
       </c>
-      <c r="C462" s="2">
+      <c r="C462">
         <v>1</v>
       </c>
     </row>
@@ -8106,7 +8105,7 @@
       <c r="B463" t="s">
         <v>461</v>
       </c>
-      <c r="C463" s="2">
+      <c r="C463">
         <v>1</v>
       </c>
     </row>
@@ -8118,7 +8117,7 @@
       <c r="B464" t="s">
         <v>462</v>
       </c>
-      <c r="C464" s="2">
+      <c r="C464">
         <v>1</v>
       </c>
     </row>
@@ -8130,7 +8129,7 @@
       <c r="B465" t="s">
         <v>463</v>
       </c>
-      <c r="C465" s="2">
+      <c r="C465">
         <v>-1</v>
       </c>
     </row>
@@ -8142,7 +8141,7 @@
       <c r="B466" t="s">
         <v>464</v>
       </c>
-      <c r="C466" s="2">
+      <c r="C466">
         <v>1</v>
       </c>
     </row>
@@ -8154,7 +8153,7 @@
       <c r="B467" t="s">
         <v>465</v>
       </c>
-      <c r="C467" s="2">
+      <c r="C467">
         <v>-1</v>
       </c>
     </row>
@@ -8166,7 +8165,7 @@
       <c r="B468" t="s">
         <v>466</v>
       </c>
-      <c r="C468" s="2">
+      <c r="C468">
         <v>1</v>
       </c>
     </row>
@@ -8178,7 +8177,7 @@
       <c r="B469" t="s">
         <v>467</v>
       </c>
-      <c r="C469" s="2">
+      <c r="C469">
         <v>-1</v>
       </c>
     </row>
@@ -8190,7 +8189,7 @@
       <c r="B470" t="s">
         <v>468</v>
       </c>
-      <c r="C470" s="2">
+      <c r="C470">
         <v>-1</v>
       </c>
     </row>
@@ -8202,7 +8201,7 @@
       <c r="B471" t="s">
         <v>469</v>
       </c>
-      <c r="C471" s="2">
+      <c r="C471">
         <v>2</v>
       </c>
     </row>
@@ -8214,7 +8213,7 @@
       <c r="B472" t="s">
         <v>470</v>
       </c>
-      <c r="C472" s="2">
+      <c r="C472">
         <v>2</v>
       </c>
     </row>
@@ -8226,7 +8225,7 @@
       <c r="B473" t="s">
         <v>471</v>
       </c>
-      <c r="C473" s="2">
+      <c r="C473">
         <v>0</v>
       </c>
     </row>
@@ -8238,7 +8237,7 @@
       <c r="B474" t="s">
         <v>472</v>
       </c>
-      <c r="C474" s="2">
+      <c r="C474">
         <v>-1</v>
       </c>
     </row>
@@ -8250,7 +8249,7 @@
       <c r="B475" t="s">
         <v>473</v>
       </c>
-      <c r="C475" s="2">
+      <c r="C475">
         <v>-1</v>
       </c>
     </row>
@@ -8262,7 +8261,7 @@
       <c r="B476" t="s">
         <v>474</v>
       </c>
-      <c r="C476" s="2">
+      <c r="C476">
         <v>-1</v>
       </c>
     </row>
@@ -8274,7 +8273,7 @@
       <c r="B477" t="s">
         <v>475</v>
       </c>
-      <c r="C477" s="2">
+      <c r="C477">
         <v>-1</v>
       </c>
     </row>
@@ -8286,7 +8285,7 @@
       <c r="B478" t="s">
         <v>476</v>
       </c>
-      <c r="C478" s="2">
+      <c r="C478">
         <v>-1</v>
       </c>
     </row>
@@ -8298,7 +8297,7 @@
       <c r="B479" t="s">
         <v>477</v>
       </c>
-      <c r="C479" s="2">
+      <c r="C479">
         <v>-1</v>
       </c>
     </row>
@@ -8310,7 +8309,7 @@
       <c r="B480" t="s">
         <v>478</v>
       </c>
-      <c r="C480" s="2">
+      <c r="C480">
         <v>0</v>
       </c>
     </row>
@@ -8322,7 +8321,7 @@
       <c r="B481" t="s">
         <v>479</v>
       </c>
-      <c r="C481" s="2">
+      <c r="C481">
         <v>1</v>
       </c>
     </row>
@@ -8334,7 +8333,7 @@
       <c r="B482" t="s">
         <v>480</v>
       </c>
-      <c r="C482" s="2">
+      <c r="C482">
         <v>-1</v>
       </c>
     </row>
@@ -8346,7 +8345,7 @@
       <c r="B483" t="s">
         <v>481</v>
       </c>
-      <c r="C483" s="2">
+      <c r="C483">
         <v>0</v>
       </c>
     </row>
@@ -8358,7 +8357,7 @@
       <c r="B484" t="s">
         <v>482</v>
       </c>
-      <c r="C484" s="2">
+      <c r="C484">
         <v>1</v>
       </c>
     </row>
@@ -8370,7 +8369,7 @@
       <c r="B485" t="s">
         <v>483</v>
       </c>
-      <c r="C485" s="2">
+      <c r="C485">
         <v>0</v>
       </c>
     </row>
@@ -8382,7 +8381,7 @@
       <c r="B486" t="s">
         <v>484</v>
       </c>
-      <c r="C486" s="2">
+      <c r="C486">
         <v>1</v>
       </c>
     </row>
@@ -8394,7 +8393,7 @@
       <c r="B487" t="s">
         <v>485</v>
       </c>
-      <c r="C487" s="2">
+      <c r="C487">
         <v>1</v>
       </c>
     </row>
@@ -8406,7 +8405,7 @@
       <c r="B488" t="s">
         <v>486</v>
       </c>
-      <c r="C488" s="2">
+      <c r="C488">
         <v>1</v>
       </c>
     </row>
@@ -8418,7 +8417,7 @@
       <c r="B489" t="s">
         <v>487</v>
       </c>
-      <c r="C489" s="2">
+      <c r="C489">
         <v>0</v>
       </c>
     </row>
@@ -8430,7 +8429,7 @@
       <c r="B490" t="s">
         <v>488</v>
       </c>
-      <c r="C490" s="2">
+      <c r="C490">
         <v>1</v>
       </c>
     </row>
@@ -8442,7 +8441,7 @@
       <c r="B491" t="s">
         <v>489</v>
       </c>
-      <c r="C491" s="2">
+      <c r="C491">
         <v>1</v>
       </c>
     </row>
@@ -8454,7 +8453,7 @@
       <c r="B492" t="s">
         <v>490</v>
       </c>
-      <c r="C492" s="2">
+      <c r="C492">
         <v>0</v>
       </c>
     </row>
@@ -8466,7 +8465,7 @@
       <c r="B493" t="s">
         <v>491</v>
       </c>
-      <c r="C493" s="2">
+      <c r="C493">
         <v>1</v>
       </c>
     </row>
@@ -8478,7 +8477,7 @@
       <c r="B494" t="s">
         <v>492</v>
       </c>
-      <c r="C494" s="2">
+      <c r="C494">
         <v>0</v>
       </c>
     </row>
@@ -8490,7 +8489,7 @@
       <c r="B495" t="s">
         <v>493</v>
       </c>
-      <c r="C495" s="2">
+      <c r="C495">
         <v>1</v>
       </c>
     </row>
@@ -8502,7 +8501,7 @@
       <c r="B496" t="s">
         <v>494</v>
       </c>
-      <c r="C496" s="2">
+      <c r="C496">
         <v>-1</v>
       </c>
     </row>
@@ -8514,7 +8513,7 @@
       <c r="B497" t="s">
         <v>495</v>
       </c>
-      <c r="C497" s="2">
+      <c r="C497">
         <v>-1</v>
       </c>
     </row>
@@ -8526,7 +8525,7 @@
       <c r="B498" t="s">
         <v>496</v>
       </c>
-      <c r="C498" s="2">
+      <c r="C498">
         <v>2</v>
       </c>
     </row>
@@ -8538,7 +8537,7 @@
       <c r="B499" t="s">
         <v>497</v>
       </c>
-      <c r="C499" s="2">
+      <c r="C499">
         <v>-1</v>
       </c>
     </row>
@@ -8550,7 +8549,7 @@
       <c r="B500" t="s">
         <v>498</v>
       </c>
-      <c r="C500" s="2">
+      <c r="C500">
         <v>2</v>
       </c>
     </row>
@@ -8562,7 +8561,7 @@
       <c r="B501" t="s">
         <v>499</v>
       </c>
-      <c r="C501" s="2">
+      <c r="C501">
         <v>-1</v>
       </c>
     </row>
@@ -8574,7 +8573,7 @@
       <c r="B502" t="s">
         <v>500</v>
       </c>
-      <c r="C502" s="2">
+      <c r="C502">
         <v>2</v>
       </c>
     </row>
@@ -8586,7 +8585,7 @@
       <c r="B503" t="s">
         <v>501</v>
       </c>
-      <c r="C503" s="2">
+      <c r="C503">
         <v>2</v>
       </c>
     </row>
@@ -8598,7 +8597,7 @@
       <c r="B504" t="s">
         <v>502</v>
       </c>
-      <c r="C504" s="2">
+      <c r="C504">
         <v>2</v>
       </c>
     </row>
@@ -8610,7 +8609,7 @@
       <c r="B505" t="s">
         <v>503</v>
       </c>
-      <c r="C505" s="2">
+      <c r="C505">
         <v>-1</v>
       </c>
     </row>
@@ -8622,7 +8621,7 @@
       <c r="B506" t="s">
         <v>504</v>
       </c>
-      <c r="C506" s="2">
+      <c r="C506">
         <v>2</v>
       </c>
     </row>
@@ -8634,7 +8633,7 @@
       <c r="B507" t="s">
         <v>505</v>
       </c>
-      <c r="C507" s="2">
+      <c r="C507">
         <v>-1</v>
       </c>
     </row>
@@ -8646,7 +8645,7 @@
       <c r="B508" t="s">
         <v>506</v>
       </c>
-      <c r="C508" s="2">
+      <c r="C508">
         <v>1</v>
       </c>
     </row>
@@ -8658,7 +8657,7 @@
       <c r="B509" t="s">
         <v>507</v>
       </c>
-      <c r="C509" s="2">
+      <c r="C509">
         <v>1</v>
       </c>
     </row>
@@ -8670,7 +8669,7 @@
       <c r="B510" t="s">
         <v>508</v>
       </c>
-      <c r="C510" s="2">
+      <c r="C510">
         <v>1</v>
       </c>
     </row>
@@ -8682,7 +8681,7 @@
       <c r="B511" t="s">
         <v>509</v>
       </c>
-      <c r="C511" s="2">
+      <c r="C511">
         <v>1</v>
       </c>
     </row>
@@ -8694,7 +8693,7 @@
       <c r="B512" t="s">
         <v>510</v>
       </c>
-      <c r="C512" s="2">
+      <c r="C512">
         <v>1</v>
       </c>
     </row>
@@ -8706,7 +8705,7 @@
       <c r="B513" t="s">
         <v>511</v>
       </c>
-      <c r="C513" s="2">
+      <c r="C513">
         <v>-1</v>
       </c>
     </row>
@@ -8718,7 +8717,7 @@
       <c r="B514" t="s">
         <v>512</v>
       </c>
-      <c r="C514" s="2">
+      <c r="C514">
         <v>-2</v>
       </c>
     </row>
@@ -8730,7 +8729,7 @@
       <c r="B515" t="s">
         <v>513</v>
       </c>
-      <c r="C515" s="2">
+      <c r="C515">
         <v>1</v>
       </c>
     </row>
@@ -8742,7 +8741,7 @@
       <c r="B516" t="s">
         <v>514</v>
       </c>
-      <c r="C516" s="2">
+      <c r="C516">
         <v>1</v>
       </c>
     </row>
@@ -8754,7 +8753,7 @@
       <c r="B517" t="s">
         <v>515</v>
       </c>
-      <c r="C517" s="2">
+      <c r="C517">
         <v>1</v>
       </c>
     </row>
@@ -8766,7 +8765,7 @@
       <c r="B518" t="s">
         <v>516</v>
       </c>
-      <c r="C518" s="2">
+      <c r="C518">
         <v>2</v>
       </c>
     </row>
@@ -8778,7 +8777,7 @@
       <c r="B519" t="s">
         <v>517</v>
       </c>
-      <c r="C519" s="2">
+      <c r="C519">
         <v>2</v>
       </c>
     </row>
@@ -8790,7 +8789,7 @@
       <c r="B520" t="s">
         <v>518</v>
       </c>
-      <c r="C520" s="2">
+      <c r="C520">
         <v>2</v>
       </c>
     </row>
@@ -8802,7 +8801,7 @@
       <c r="B521" t="s">
         <v>519</v>
       </c>
-      <c r="C521" s="2">
+      <c r="C521">
         <v>2</v>
       </c>
     </row>
@@ -8814,7 +8813,7 @@
       <c r="B522" t="s">
         <v>520</v>
       </c>
-      <c r="C522" s="2">
+      <c r="C522">
         <v>-2</v>
       </c>
     </row>
@@ -8826,7 +8825,7 @@
       <c r="B523" t="s">
         <v>521</v>
       </c>
-      <c r="C523" s="2">
+      <c r="C523">
         <v>2</v>
       </c>
     </row>
@@ -8838,7 +8837,7 @@
       <c r="B524" t="s">
         <v>522</v>
       </c>
-      <c r="C524" s="2">
+      <c r="C524">
         <v>-2</v>
       </c>
     </row>
@@ -8850,7 +8849,7 @@
       <c r="B525" t="s">
         <v>523</v>
       </c>
-      <c r="C525" s="2">
+      <c r="C525">
         <v>1</v>
       </c>
     </row>
@@ -8862,7 +8861,7 @@
       <c r="B526" t="s">
         <v>524</v>
       </c>
-      <c r="C526" s="2">
+      <c r="C526">
         <v>-1</v>
       </c>
     </row>
@@ -8874,7 +8873,7 @@
       <c r="B527" t="s">
         <v>525</v>
       </c>
-      <c r="C527" s="2">
+      <c r="C527">
         <v>2</v>
       </c>
     </row>
@@ -8886,7 +8885,7 @@
       <c r="B528" t="s">
         <v>526</v>
       </c>
-      <c r="C528" s="2">
+      <c r="C528">
         <v>1</v>
       </c>
     </row>
@@ -8898,7 +8897,7 @@
       <c r="B529" t="s">
         <v>526</v>
       </c>
-      <c r="C529" s="2">
+      <c r="C529">
         <v>-1</v>
       </c>
     </row>
@@ -8910,7 +8909,7 @@
       <c r="B530" t="s">
         <v>527</v>
       </c>
-      <c r="C530" s="2">
+      <c r="C530">
         <v>1</v>
       </c>
     </row>
@@ -8922,7 +8921,7 @@
       <c r="B531" t="s">
         <v>528</v>
       </c>
-      <c r="C531" s="2">
+      <c r="C531">
         <v>1</v>
       </c>
     </row>
@@ -8934,7 +8933,7 @@
       <c r="B532" t="s">
         <v>529</v>
       </c>
-      <c r="C532" s="2">
+      <c r="C532">
         <v>-1</v>
       </c>
     </row>
@@ -8946,7 +8945,7 @@
       <c r="B533" t="s">
         <v>530</v>
       </c>
-      <c r="C533" s="2">
+      <c r="C533">
         <v>1</v>
       </c>
     </row>
@@ -8958,7 +8957,7 @@
       <c r="B534" t="s">
         <v>531</v>
       </c>
-      <c r="C534" s="2">
+      <c r="C534">
         <v>1</v>
       </c>
     </row>
@@ -8970,7 +8969,7 @@
       <c r="B535" t="s">
         <v>532</v>
       </c>
-      <c r="C535" s="2">
+      <c r="C535">
         <v>1</v>
       </c>
     </row>
@@ -8982,7 +8981,7 @@
       <c r="B536" t="s">
         <v>533</v>
       </c>
-      <c r="C536" s="2">
+      <c r="C536">
         <v>1</v>
       </c>
     </row>
@@ -8994,7 +8993,7 @@
       <c r="B537" t="s">
         <v>534</v>
       </c>
-      <c r="C537" s="2">
+      <c r="C537">
         <v>1</v>
       </c>
     </row>
@@ -9006,7 +9005,7 @@
       <c r="B538" t="s">
         <v>535</v>
       </c>
-      <c r="C538" s="2">
+      <c r="C538">
         <v>0</v>
       </c>
     </row>
@@ -9018,7 +9017,7 @@
       <c r="B539" t="s">
         <v>536</v>
       </c>
-      <c r="C539" s="2">
+      <c r="C539">
         <v>2</v>
       </c>
     </row>
@@ -9030,7 +9029,7 @@
       <c r="B540" t="s">
         <v>537</v>
       </c>
-      <c r="C540" s="2">
+      <c r="C540">
         <v>-2</v>
       </c>
     </row>
@@ -9042,7 +9041,7 @@
       <c r="B541" t="s">
         <v>538</v>
       </c>
-      <c r="C541" s="2">
+      <c r="C541">
         <v>1</v>
       </c>
     </row>
@@ -9054,7 +9053,7 @@
       <c r="B542" t="s">
         <v>539</v>
       </c>
-      <c r="C542" s="2">
+      <c r="C542">
         <v>-2</v>
       </c>
     </row>
@@ -9066,7 +9065,7 @@
       <c r="B543" t="s">
         <v>540</v>
       </c>
-      <c r="C543" s="2">
+      <c r="C543">
         <v>-2</v>
       </c>
     </row>
@@ -9078,7 +9077,7 @@
       <c r="B544" t="s">
         <v>541</v>
       </c>
-      <c r="C544" s="2">
+      <c r="C544">
         <v>-2</v>
       </c>
     </row>
@@ -9090,7 +9089,7 @@
       <c r="B545" t="s">
         <v>542</v>
       </c>
-      <c r="C545" s="2">
+      <c r="C545">
         <v>-1</v>
       </c>
     </row>
@@ -9102,7 +9101,7 @@
       <c r="B546" t="s">
         <v>543</v>
       </c>
-      <c r="C546" s="2">
+      <c r="C546">
         <v>1</v>
       </c>
     </row>
@@ -9114,7 +9113,7 @@
       <c r="B547" t="s">
         <v>544</v>
       </c>
-      <c r="C547" s="2">
+      <c r="C547">
         <v>-1</v>
       </c>
     </row>
@@ -9126,7 +9125,7 @@
       <c r="B548" t="s">
         <v>545</v>
       </c>
-      <c r="C548" s="2">
+      <c r="C548">
         <v>-1</v>
       </c>
     </row>
@@ -9138,7 +9137,7 @@
       <c r="B549" t="s">
         <v>546</v>
       </c>
-      <c r="C549" s="2">
+      <c r="C549">
         <v>1</v>
       </c>
     </row>
@@ -9150,7 +9149,7 @@
       <c r="B550" t="s">
         <v>547</v>
       </c>
-      <c r="C550" s="2">
+      <c r="C550">
         <v>-1</v>
       </c>
     </row>
@@ -9162,7 +9161,7 @@
       <c r="B551" t="s">
         <v>548</v>
       </c>
-      <c r="C551" s="2">
+      <c r="C551">
         <v>-1</v>
       </c>
     </row>
@@ -9174,7 +9173,7 @@
       <c r="B552" t="s">
         <v>549</v>
       </c>
-      <c r="C552" s="2">
+      <c r="C552">
         <v>1</v>
       </c>
     </row>
@@ -9186,7 +9185,7 @@
       <c r="B553" t="s">
         <v>550</v>
       </c>
-      <c r="C553" s="2">
+      <c r="C553">
         <v>-1</v>
       </c>
     </row>
@@ -9198,7 +9197,7 @@
       <c r="B554" t="s">
         <v>551</v>
       </c>
-      <c r="C554" s="2">
+      <c r="C554">
         <v>-1</v>
       </c>
     </row>
@@ -9210,7 +9209,7 @@
       <c r="B555" t="s">
         <v>552</v>
       </c>
-      <c r="C555" s="2">
+      <c r="C555">
         <v>1</v>
       </c>
     </row>
@@ -9222,7 +9221,7 @@
       <c r="B556" t="s">
         <v>553</v>
       </c>
-      <c r="C556" s="2">
+      <c r="C556">
         <v>-1</v>
       </c>
     </row>
@@ -9234,7 +9233,7 @@
       <c r="B557" t="s">
         <v>554</v>
       </c>
-      <c r="C557" s="2">
+      <c r="C557">
         <v>1</v>
       </c>
     </row>
@@ -9246,7 +9245,7 @@
       <c r="B558" t="s">
         <v>555</v>
       </c>
-      <c r="C558" s="2">
+      <c r="C558">
         <v>-1</v>
       </c>
     </row>
@@ -9258,7 +9257,7 @@
       <c r="B559" t="s">
         <v>556</v>
       </c>
-      <c r="C559" s="2">
+      <c r="C559">
         <v>1</v>
       </c>
     </row>
@@ -9270,7 +9269,7 @@
       <c r="B560" t="s">
         <v>557</v>
       </c>
-      <c r="C560" s="2">
+      <c r="C560">
         <v>1</v>
       </c>
     </row>
@@ -9282,7 +9281,7 @@
       <c r="B561" t="s">
         <v>558</v>
       </c>
-      <c r="C561" s="2">
+      <c r="C561">
         <v>-1</v>
       </c>
     </row>
@@ -9294,7 +9293,7 @@
       <c r="B562" t="s">
         <v>559</v>
       </c>
-      <c r="C562" s="2">
+      <c r="C562">
         <v>1</v>
       </c>
     </row>
@@ -9306,7 +9305,7 @@
       <c r="B563" t="s">
         <v>560</v>
       </c>
-      <c r="C563" s="2">
+      <c r="C563">
         <v>-1</v>
       </c>
     </row>
@@ -9318,7 +9317,7 @@
       <c r="B564" t="s">
         <v>561</v>
       </c>
-      <c r="C564" s="2">
+      <c r="C564">
         <v>1</v>
       </c>
     </row>
@@ -9330,7 +9329,7 @@
       <c r="B565" t="s">
         <v>562</v>
       </c>
-      <c r="C565" s="2">
+      <c r="C565">
         <v>-1</v>
       </c>
     </row>
@@ -9342,7 +9341,7 @@
       <c r="B566" t="s">
         <v>563</v>
       </c>
-      <c r="C566" s="2">
+      <c r="C566">
         <v>-1</v>
       </c>
     </row>
@@ -9354,7 +9353,7 @@
       <c r="B567" t="s">
         <v>564</v>
       </c>
-      <c r="C567" s="2">
+      <c r="C567">
         <v>1</v>
       </c>
     </row>
@@ -9366,7 +9365,7 @@
       <c r="B568" t="s">
         <v>565</v>
       </c>
-      <c r="C568" s="2">
+      <c r="C568">
         <v>1</v>
       </c>
     </row>
@@ -9378,7 +9377,7 @@
       <c r="B569" t="s">
         <v>566</v>
       </c>
-      <c r="C569" s="2">
+      <c r="C569">
         <v>-1</v>
       </c>
     </row>
@@ -9390,7 +9389,7 @@
       <c r="B570" t="s">
         <v>567</v>
       </c>
-      <c r="C570" s="2">
+      <c r="C570">
         <v>-1</v>
       </c>
     </row>
@@ -9402,7 +9401,7 @@
       <c r="B571" t="s">
         <v>568</v>
       </c>
-      <c r="C571" s="2">
+      <c r="C571">
         <v>1</v>
       </c>
     </row>
@@ -9414,7 +9413,7 @@
       <c r="B572" t="s">
         <v>569</v>
       </c>
-      <c r="C572" s="2">
+      <c r="C572">
         <v>-1</v>
       </c>
     </row>
@@ -9426,7 +9425,7 @@
       <c r="B573" t="s">
         <v>570</v>
       </c>
-      <c r="C573" s="2">
+      <c r="C573">
         <v>-1</v>
       </c>
     </row>
@@ -9438,7 +9437,7 @@
       <c r="B574" t="s">
         <v>571</v>
       </c>
-      <c r="C574" s="2">
+      <c r="C574">
         <v>1</v>
       </c>
     </row>
@@ -9450,7 +9449,7 @@
       <c r="B575" t="s">
         <v>572</v>
       </c>
-      <c r="C575" s="2">
+      <c r="C575">
         <v>-1</v>
       </c>
     </row>
@@ -9462,7 +9461,7 @@
       <c r="B576" t="s">
         <v>573</v>
       </c>
-      <c r="C576" s="2">
+      <c r="C576">
         <v>2</v>
       </c>
     </row>
@@ -9474,7 +9473,7 @@
       <c r="B577" t="s">
         <v>574</v>
       </c>
-      <c r="C577" s="2">
+      <c r="C577">
         <v>-1</v>
       </c>
     </row>
@@ -9486,7 +9485,7 @@
       <c r="B578" t="s">
         <v>575</v>
       </c>
-      <c r="C578" s="2">
+      <c r="C578">
         <v>-1</v>
       </c>
     </row>
@@ -9498,7 +9497,7 @@
       <c r="B579" t="s">
         <v>576</v>
       </c>
-      <c r="C579" s="2">
+      <c r="C579">
         <v>-1</v>
       </c>
     </row>
@@ -9510,7 +9509,7 @@
       <c r="B580" t="s">
         <v>577</v>
       </c>
-      <c r="C580" s="2">
+      <c r="C580">
         <v>1</v>
       </c>
     </row>
@@ -9522,7 +9521,7 @@
       <c r="B581" t="s">
         <v>578</v>
       </c>
-      <c r="C581" s="2">
+      <c r="C581">
         <v>1</v>
       </c>
     </row>
@@ -9534,7 +9533,7 @@
       <c r="B582" t="s">
         <v>579</v>
       </c>
-      <c r="C582" s="2">
+      <c r="C582">
         <v>-1</v>
       </c>
     </row>
@@ -9546,7 +9545,7 @@
       <c r="B583" t="s">
         <v>580</v>
       </c>
-      <c r="C583" s="2">
+      <c r="C583">
         <v>2</v>
       </c>
     </row>
@@ -9558,7 +9557,7 @@
       <c r="B584" t="s">
         <v>581</v>
       </c>
-      <c r="C584" s="2">
+      <c r="C584">
         <v>-1</v>
       </c>
     </row>
@@ -9570,7 +9569,7 @@
       <c r="B585" t="s">
         <v>582</v>
       </c>
-      <c r="C585" s="2">
+      <c r="C585">
         <v>1</v>
       </c>
     </row>
@@ -9582,7 +9581,7 @@
       <c r="B586" t="s">
         <v>583</v>
       </c>
-      <c r="C586" s="2">
+      <c r="C586">
         <v>2</v>
       </c>
     </row>
@@ -9594,7 +9593,7 @@
       <c r="B587" t="s">
         <v>584</v>
       </c>
-      <c r="C587" s="2">
+      <c r="C587">
         <v>2</v>
       </c>
     </row>
@@ -9606,7 +9605,7 @@
       <c r="B588" t="s">
         <v>585</v>
       </c>
-      <c r="C588" s="2">
+      <c r="C588">
         <v>0</v>
       </c>
     </row>
@@ -9618,7 +9617,7 @@
       <c r="B589" t="s">
         <v>586</v>
       </c>
-      <c r="C589" s="2">
+      <c r="C589">
         <v>2</v>
       </c>
     </row>
@@ -9630,7 +9629,7 @@
       <c r="B590" t="s">
         <v>587</v>
       </c>
-      <c r="C590" s="2">
+      <c r="C590">
         <v>0</v>
       </c>
     </row>
@@ -9642,7 +9641,7 @@
       <c r="B591" t="s">
         <v>588</v>
       </c>
-      <c r="C591" s="2">
+      <c r="C591">
         <v>0</v>
       </c>
     </row>
@@ -9654,7 +9653,7 @@
       <c r="B592" t="s">
         <v>589</v>
       </c>
-      <c r="C592" s="2">
+      <c r="C592">
         <v>-1</v>
       </c>
     </row>
@@ -9666,7 +9665,7 @@
       <c r="B593" t="s">
         <v>590</v>
       </c>
-      <c r="C593" s="2">
+      <c r="C593">
         <v>-1</v>
       </c>
     </row>
@@ -9678,7 +9677,7 @@
       <c r="B594" t="s">
         <v>591</v>
       </c>
-      <c r="C594" s="2">
+      <c r="C594">
         <v>1</v>
       </c>
     </row>
@@ -9690,7 +9689,7 @@
       <c r="B595" t="s">
         <v>592</v>
       </c>
-      <c r="C595" s="2">
+      <c r="C595">
         <v>-1</v>
       </c>
     </row>
@@ -9702,7 +9701,7 @@
       <c r="B596" t="s">
         <v>593</v>
       </c>
-      <c r="C596" s="2">
+      <c r="C596">
         <v>1</v>
       </c>
     </row>
@@ -9714,7 +9713,7 @@
       <c r="B597" t="s">
         <v>594</v>
       </c>
-      <c r="C597" s="2">
+      <c r="C597">
         <v>-1</v>
       </c>
     </row>
@@ -9726,7 +9725,7 @@
       <c r="B598" t="s">
         <v>595</v>
       </c>
-      <c r="C598" s="2">
+      <c r="C598">
         <v>-1</v>
       </c>
     </row>
@@ -9738,7 +9737,7 @@
       <c r="B599" t="s">
         <v>596</v>
       </c>
-      <c r="C599" s="2">
+      <c r="C599">
         <v>-1</v>
       </c>
     </row>
@@ -9750,7 +9749,7 @@
       <c r="B600" t="s">
         <v>597</v>
       </c>
-      <c r="C600" s="2">
+      <c r="C600">
         <v>1</v>
       </c>
     </row>
@@ -9762,7 +9761,7 @@
       <c r="B601" t="s">
         <v>598</v>
       </c>
-      <c r="C601" s="2">
+      <c r="C601">
         <v>-1</v>
       </c>
     </row>
@@ -9774,7 +9773,7 @@
       <c r="B602" t="s">
         <v>599</v>
       </c>
-      <c r="C602" s="2">
+      <c r="C602">
         <v>-1</v>
       </c>
     </row>
@@ -9786,7 +9785,7 @@
       <c r="B603" t="s">
         <v>600</v>
       </c>
-      <c r="C603" s="2">
+      <c r="C603">
         <v>1</v>
       </c>
     </row>
@@ -9798,7 +9797,7 @@
       <c r="B604" t="s">
         <v>601</v>
       </c>
-      <c r="C604" s="2">
+      <c r="C604">
         <v>-1</v>
       </c>
     </row>
@@ -9810,7 +9809,7 @@
       <c r="B605" t="s">
         <v>602</v>
       </c>
-      <c r="C605" s="2">
+      <c r="C605">
         <v>2</v>
       </c>
     </row>
@@ -9822,7 +9821,7 @@
       <c r="B606" t="s">
         <v>603</v>
       </c>
-      <c r="C606" s="2">
+      <c r="C606">
         <v>0</v>
       </c>
     </row>
@@ -9834,7 +9833,7 @@
       <c r="B607" t="s">
         <v>604</v>
       </c>
-      <c r="C607" s="2">
+      <c r="C607">
         <v>-1</v>
       </c>
     </row>
@@ -9846,7 +9845,7 @@
       <c r="B608" t="s">
         <v>605</v>
       </c>
-      <c r="C608" s="2">
+      <c r="C608">
         <v>-1</v>
       </c>
     </row>
@@ -9858,7 +9857,7 @@
       <c r="B609" t="s">
         <v>606</v>
       </c>
-      <c r="C609" s="2">
+      <c r="C609">
         <v>-1</v>
       </c>
     </row>
@@ -9870,7 +9869,7 @@
       <c r="B610" t="s">
         <v>607</v>
       </c>
-      <c r="C610" s="2">
+      <c r="C610">
         <v>1</v>
       </c>
     </row>
@@ -9882,7 +9881,7 @@
       <c r="B611" t="s">
         <v>608</v>
       </c>
-      <c r="C611" s="2">
+      <c r="C611">
         <v>-1</v>
       </c>
     </row>
@@ -9894,7 +9893,7 @@
       <c r="B612" t="s">
         <v>609</v>
       </c>
-      <c r="C612" s="2">
+      <c r="C612">
         <v>-1</v>
       </c>
     </row>
@@ -9906,7 +9905,7 @@
       <c r="B613" t="s">
         <v>610</v>
       </c>
-      <c r="C613" s="2">
+      <c r="C613">
         <v>-1</v>
       </c>
     </row>
@@ -9918,7 +9917,7 @@
       <c r="B614" t="s">
         <v>611</v>
       </c>
-      <c r="C614" s="2">
+      <c r="C614">
         <v>0</v>
       </c>
     </row>
@@ -9930,7 +9929,7 @@
       <c r="B615" t="s">
         <v>612</v>
       </c>
-      <c r="C615" s="2">
+      <c r="C615">
         <v>-1</v>
       </c>
     </row>
@@ -9942,7 +9941,7 @@
       <c r="B616" t="s">
         <v>613</v>
       </c>
-      <c r="C616" s="2">
+      <c r="C616">
         <v>0</v>
       </c>
     </row>
@@ -9954,7 +9953,7 @@
       <c r="B617" t="s">
         <v>614</v>
       </c>
-      <c r="C617" s="2">
+      <c r="C617">
         <v>0</v>
       </c>
     </row>
@@ -9966,7 +9965,7 @@
       <c r="B618" t="s">
         <v>615</v>
       </c>
-      <c r="C618" s="2">
+      <c r="C618">
         <v>0</v>
       </c>
     </row>
@@ -9978,7 +9977,7 @@
       <c r="B619" t="s">
         <v>616</v>
       </c>
-      <c r="C619" s="2">
+      <c r="C619">
         <v>-1</v>
       </c>
     </row>
@@ -9990,7 +9989,7 @@
       <c r="B620" t="s">
         <v>617</v>
       </c>
-      <c r="C620" s="2">
+      <c r="C620">
         <v>0</v>
       </c>
     </row>
@@ -10002,7 +10001,7 @@
       <c r="B621" t="s">
         <v>618</v>
       </c>
-      <c r="C621" s="2">
+      <c r="C621">
         <v>0</v>
       </c>
     </row>
@@ -10014,7 +10013,7 @@
       <c r="B622" t="s">
         <v>619</v>
       </c>
-      <c r="C622" s="2">
+      <c r="C622">
         <v>-1</v>
       </c>
     </row>
@@ -10026,7 +10025,7 @@
       <c r="B623" t="s">
         <v>620</v>
       </c>
-      <c r="C623" s="2">
+      <c r="C623">
         <v>2</v>
       </c>
     </row>
@@ -10038,7 +10037,7 @@
       <c r="B624" t="s">
         <v>621</v>
       </c>
-      <c r="C624" s="2">
+      <c r="C624">
         <v>-1</v>
       </c>
     </row>
@@ -10050,7 +10049,7 @@
       <c r="B625" t="s">
         <v>622</v>
       </c>
-      <c r="C625" s="2">
+      <c r="C625">
         <v>2</v>
       </c>
     </row>
@@ -10062,7 +10061,7 @@
       <c r="B626" t="s">
         <v>623</v>
       </c>
-      <c r="C626" s="2">
+      <c r="C626">
         <v>1</v>
       </c>
     </row>
@@ -10074,7 +10073,7 @@
       <c r="B627" t="s">
         <v>624</v>
       </c>
-      <c r="C627" s="2">
+      <c r="C627">
         <v>-1</v>
       </c>
     </row>
@@ -10086,7 +10085,7 @@
       <c r="B628" t="s">
         <v>625</v>
       </c>
-      <c r="C628" s="2">
+      <c r="C628">
         <v>-1</v>
       </c>
     </row>
@@ -10098,7 +10097,7 @@
       <c r="B629" t="s">
         <v>626</v>
       </c>
-      <c r="C629" s="2">
+      <c r="C629">
         <v>-1</v>
       </c>
     </row>
@@ -10110,7 +10109,7 @@
       <c r="B630" t="s">
         <v>627</v>
       </c>
-      <c r="C630" s="2">
+      <c r="C630">
         <v>1</v>
       </c>
     </row>
@@ -10122,7 +10121,7 @@
       <c r="B631" t="s">
         <v>628</v>
       </c>
-      <c r="C631" s="2">
+      <c r="C631">
         <v>-1</v>
       </c>
     </row>
@@ -10134,7 +10133,7 @@
       <c r="B632" t="s">
         <v>629</v>
       </c>
-      <c r="C632" s="2">
+      <c r="C632">
         <v>1</v>
       </c>
     </row>
@@ -10146,7 +10145,7 @@
       <c r="B633" t="s">
         <v>630</v>
       </c>
-      <c r="C633" s="2">
+      <c r="C633">
         <v>0</v>
       </c>
     </row>
@@ -10158,7 +10157,7 @@
       <c r="B634" t="s">
         <v>631</v>
       </c>
-      <c r="C634" s="2">
+      <c r="C634">
         <v>0</v>
       </c>
     </row>
@@ -10170,7 +10169,7 @@
       <c r="B635" t="s">
         <v>632</v>
       </c>
-      <c r="C635" s="2">
+      <c r="C635">
         <v>0</v>
       </c>
     </row>
@@ -10182,7 +10181,7 @@
       <c r="B636" t="s">
         <v>633</v>
       </c>
-      <c r="C636" s="2">
+      <c r="C636">
         <v>-1</v>
       </c>
     </row>
@@ -10194,7 +10193,7 @@
       <c r="B637" t="s">
         <v>634</v>
       </c>
-      <c r="C637" s="2">
+      <c r="C637">
         <v>-1</v>
       </c>
     </row>
@@ -10206,7 +10205,7 @@
       <c r="B638" t="s">
         <v>635</v>
       </c>
-      <c r="C638" s="2">
+      <c r="C638">
         <v>1</v>
       </c>
     </row>
@@ -10218,7 +10217,7 @@
       <c r="B639" t="s">
         <v>636</v>
       </c>
-      <c r="C639" s="2">
+      <c r="C639">
         <v>-1</v>
       </c>
     </row>
@@ -10230,7 +10229,7 @@
       <c r="B640" t="s">
         <v>637</v>
       </c>
-      <c r="C640" s="2">
+      <c r="C640">
         <v>0</v>
       </c>
     </row>
@@ -10242,7 +10241,7 @@
       <c r="B641" t="s">
         <v>638</v>
       </c>
-      <c r="C641" s="2">
+      <c r="C641">
         <v>0</v>
       </c>
     </row>
@@ -10254,7 +10253,7 @@
       <c r="B642" t="s">
         <v>639</v>
       </c>
-      <c r="C642" s="2">
+      <c r="C642">
         <v>0</v>
       </c>
     </row>
@@ -10266,7 +10265,7 @@
       <c r="B643" t="s">
         <v>640</v>
       </c>
-      <c r="C643" s="2">
+      <c r="C643">
         <v>1</v>
       </c>
     </row>
@@ -10278,7 +10277,7 @@
       <c r="B644" t="s">
         <v>641</v>
       </c>
-      <c r="C644" s="2">
+      <c r="C644">
         <v>0</v>
       </c>
     </row>
@@ -10290,7 +10289,7 @@
       <c r="B645" t="s">
         <v>642</v>
       </c>
-      <c r="C645" s="2">
+      <c r="C645">
         <v>0</v>
       </c>
     </row>
@@ -10302,7 +10301,7 @@
       <c r="B646" t="s">
         <v>643</v>
       </c>
-      <c r="C646" s="2">
+      <c r="C646">
         <v>0</v>
       </c>
     </row>
@@ -10314,7 +10313,7 @@
       <c r="B647" t="s">
         <v>644</v>
       </c>
-      <c r="C647" s="2">
+      <c r="C647">
         <v>0</v>
       </c>
     </row>
@@ -10326,7 +10325,7 @@
       <c r="B648" t="s">
         <v>645</v>
       </c>
-      <c r="C648" s="2">
+      <c r="C648">
         <v>0</v>
       </c>
     </row>
@@ -10338,7 +10337,7 @@
       <c r="B649" t="s">
         <v>646</v>
       </c>
-      <c r="C649" s="2">
+      <c r="C649">
         <v>-1</v>
       </c>
     </row>
@@ -10350,7 +10349,7 @@
       <c r="B650" t="s">
         <v>647</v>
       </c>
-      <c r="C650" s="2">
+      <c r="C650">
         <v>-1</v>
       </c>
     </row>
@@ -10362,7 +10361,7 @@
       <c r="B651" t="s">
         <v>648</v>
       </c>
-      <c r="C651" s="2">
+      <c r="C651">
         <v>0</v>
       </c>
     </row>
@@ -10374,7 +10373,7 @@
       <c r="B652" t="s">
         <v>649</v>
       </c>
-      <c r="C652" s="2">
+      <c r="C652">
         <v>0</v>
       </c>
     </row>
@@ -10386,7 +10385,7 @@
       <c r="B653" t="s">
         <v>650</v>
       </c>
-      <c r="C653" s="2">
+      <c r="C653">
         <v>0</v>
       </c>
     </row>
@@ -10398,7 +10397,7 @@
       <c r="B654" t="s">
         <v>651</v>
       </c>
-      <c r="C654" s="2">
+      <c r="C654">
         <v>0</v>
       </c>
     </row>
@@ -10410,7 +10409,7 @@
       <c r="B655" t="s">
         <v>652</v>
       </c>
-      <c r="C655" s="2">
+      <c r="C655">
         <v>0</v>
       </c>
     </row>
@@ -10422,7 +10421,7 @@
       <c r="B656" t="s">
         <v>653</v>
       </c>
-      <c r="C656" s="2">
+      <c r="C656">
         <v>0</v>
       </c>
     </row>
@@ -10434,7 +10433,7 @@
       <c r="B657" t="s">
         <v>654</v>
       </c>
-      <c r="C657" s="2">
+      <c r="C657">
         <v>0</v>
       </c>
     </row>
@@ -10446,7 +10445,7 @@
       <c r="B658" t="s">
         <v>655</v>
       </c>
-      <c r="C658" s="2">
+      <c r="C658">
         <v>0</v>
       </c>
     </row>
@@ -10458,7 +10457,7 @@
       <c r="B659" t="s">
         <v>656</v>
       </c>
-      <c r="C659" s="2">
+      <c r="C659">
         <v>0</v>
       </c>
     </row>
@@ -10470,7 +10469,7 @@
       <c r="B660" t="s">
         <v>657</v>
       </c>
-      <c r="C660" s="2">
+      <c r="C660">
         <v>0</v>
       </c>
     </row>
@@ -10482,7 +10481,7 @@
       <c r="B661" t="s">
         <v>658</v>
       </c>
-      <c r="C661" s="2">
+      <c r="C661">
         <v>0</v>
       </c>
     </row>
@@ -10494,7 +10493,7 @@
       <c r="B662" t="s">
         <v>659</v>
       </c>
-      <c r="C662" s="2">
+      <c r="C662">
         <v>0</v>
       </c>
     </row>
@@ -10506,7 +10505,7 @@
       <c r="B663" t="s">
         <v>660</v>
       </c>
-      <c r="C663" s="2">
+      <c r="C663">
         <v>0</v>
       </c>
     </row>
@@ -10518,7 +10517,7 @@
       <c r="B664" t="s">
         <v>661</v>
       </c>
-      <c r="C664" s="2">
+      <c r="C664">
         <v>0</v>
       </c>
     </row>
@@ -10530,7 +10529,7 @@
       <c r="B665" t="s">
         <v>662</v>
       </c>
-      <c r="C665" s="2">
+      <c r="C665">
         <v>0</v>
       </c>
     </row>
@@ -10542,7 +10541,7 @@
       <c r="B666" t="s">
         <v>663</v>
       </c>
-      <c r="C666" s="2">
+      <c r="C666">
         <v>0</v>
       </c>
     </row>
@@ -10554,7 +10553,7 @@
       <c r="B667" t="s">
         <v>664</v>
       </c>
-      <c r="C667" s="2">
+      <c r="C667">
         <v>0</v>
       </c>
     </row>
@@ -10566,7 +10565,7 @@
       <c r="B668" t="s">
         <v>665</v>
       </c>
-      <c r="C668" s="2">
+      <c r="C668">
         <v>0</v>
       </c>
     </row>
@@ -10578,7 +10577,7 @@
       <c r="B669" t="s">
         <v>666</v>
       </c>
-      <c r="C669" s="2">
+      <c r="C669">
         <v>0</v>
       </c>
     </row>
@@ -10590,7 +10589,7 @@
       <c r="B670" t="s">
         <v>667</v>
       </c>
-      <c r="C670" s="2">
+      <c r="C670">
         <v>-1</v>
       </c>
     </row>
@@ -10602,7 +10601,7 @@
       <c r="B671" t="s">
         <v>668</v>
       </c>
-      <c r="C671" s="2">
+      <c r="C671">
         <v>0</v>
       </c>
     </row>
@@ -10614,7 +10613,7 @@
       <c r="B672" t="s">
         <v>669</v>
       </c>
-      <c r="C672" s="2">
+      <c r="C672">
         <v>0</v>
       </c>
     </row>
@@ -10626,7 +10625,7 @@
       <c r="B673" t="s">
         <v>670</v>
       </c>
-      <c r="C673" s="2">
+      <c r="C673">
         <v>0</v>
       </c>
     </row>
@@ -10638,7 +10637,7 @@
       <c r="B674" t="s">
         <v>671</v>
       </c>
-      <c r="C674" s="2">
+      <c r="C674">
         <v>0</v>
       </c>
     </row>
@@ -10650,7 +10649,7 @@
       <c r="B675" t="s">
         <v>672</v>
       </c>
-      <c r="C675" s="2">
+      <c r="C675">
         <v>0</v>
       </c>
     </row>
@@ -10662,7 +10661,7 @@
       <c r="B676" t="s">
         <v>673</v>
       </c>
-      <c r="C676" s="2">
+      <c r="C676">
         <v>0</v>
       </c>
     </row>
@@ -10674,7 +10673,7 @@
       <c r="B677" t="s">
         <v>674</v>
       </c>
-      <c r="C677" s="2">
+      <c r="C677">
         <v>0</v>
       </c>
     </row>
@@ -10686,7 +10685,7 @@
       <c r="B678" t="s">
         <v>675</v>
       </c>
-      <c r="C678" s="2">
+      <c r="C678">
         <v>0</v>
       </c>
     </row>
@@ -10698,7 +10697,7 @@
       <c r="B679" t="s">
         <v>676</v>
       </c>
-      <c r="C679" s="2">
+      <c r="C679">
         <v>0</v>
       </c>
     </row>
@@ -10710,7 +10709,7 @@
       <c r="B680" t="s">
         <v>677</v>
       </c>
-      <c r="C680" s="2">
+      <c r="C680">
         <v>0</v>
       </c>
     </row>
@@ -10722,7 +10721,7 @@
       <c r="B681" t="s">
         <v>678</v>
       </c>
-      <c r="C681" s="2">
+      <c r="C681">
         <v>0</v>
       </c>
     </row>
@@ -10734,7 +10733,7 @@
       <c r="B682" t="s">
         <v>679</v>
       </c>
-      <c r="C682" s="2">
+      <c r="C682">
         <v>0</v>
       </c>
     </row>
@@ -10746,7 +10745,7 @@
       <c r="B683" t="s">
         <v>680</v>
       </c>
-      <c r="C683" s="2">
+      <c r="C683">
         <v>0</v>
       </c>
     </row>
@@ -10758,7 +10757,7 @@
       <c r="B684" t="s">
         <v>681</v>
       </c>
-      <c r="C684" s="2">
+      <c r="C684">
         <v>0</v>
       </c>
     </row>
@@ -10770,7 +10769,7 @@
       <c r="B685" t="s">
         <v>682</v>
       </c>
-      <c r="C685" s="2">
+      <c r="C685">
         <v>0</v>
       </c>
     </row>
@@ -10782,7 +10781,7 @@
       <c r="B686" t="s">
         <v>683</v>
       </c>
-      <c r="C686" s="2">
+      <c r="C686">
         <v>0</v>
       </c>
     </row>
@@ -10794,7 +10793,7 @@
       <c r="B687" t="s">
         <v>684</v>
       </c>
-      <c r="C687" s="2">
+      <c r="C687">
         <v>0</v>
       </c>
     </row>
@@ -10806,7 +10805,7 @@
       <c r="B688" t="s">
         <v>685</v>
       </c>
-      <c r="C688" s="2">
+      <c r="C688">
         <v>0</v>
       </c>
     </row>
@@ -10818,7 +10817,7 @@
       <c r="B689" t="s">
         <v>686</v>
       </c>
-      <c r="C689" s="2">
+      <c r="C689">
         <v>0</v>
       </c>
     </row>
@@ -10830,7 +10829,7 @@
       <c r="B690" t="s">
         <v>687</v>
       </c>
-      <c r="C690" s="2">
+      <c r="C690">
         <v>0</v>
       </c>
     </row>
@@ -10842,7 +10841,7 @@
       <c r="B691" t="s">
         <v>688</v>
       </c>
-      <c r="C691" s="2">
+      <c r="C691">
         <v>0</v>
       </c>
     </row>
@@ -10854,7 +10853,7 @@
       <c r="B692" t="s">
         <v>689</v>
       </c>
-      <c r="C692" s="2">
+      <c r="C692">
         <v>0</v>
       </c>
     </row>
@@ -10866,7 +10865,7 @@
       <c r="B693" t="s">
         <v>690</v>
       </c>
-      <c r="C693" s="2">
+      <c r="C693">
         <v>-1</v>
       </c>
     </row>
@@ -10878,7 +10877,7 @@
       <c r="B694" t="s">
         <v>691</v>
       </c>
-      <c r="C694" s="2">
+      <c r="C694">
         <v>-1</v>
       </c>
     </row>
@@ -10890,7 +10889,7 @@
       <c r="B695" t="s">
         <v>692</v>
       </c>
-      <c r="C695" s="2">
+      <c r="C695">
         <v>-1</v>
       </c>
     </row>
@@ -10902,7 +10901,7 @@
       <c r="B696" t="s">
         <v>693</v>
       </c>
-      <c r="C696" s="2">
+      <c r="C696">
         <v>-1</v>
       </c>
     </row>
@@ -10914,7 +10913,7 @@
       <c r="B697" t="s">
         <v>694</v>
       </c>
-      <c r="C697" s="2">
+      <c r="C697">
         <v>0</v>
       </c>
     </row>
@@ -10926,7 +10925,7 @@
       <c r="B698" t="s">
         <v>695</v>
       </c>
-      <c r="C698" s="2">
+      <c r="C698">
         <v>0</v>
       </c>
     </row>
@@ -10938,7 +10937,7 @@
       <c r="B699" t="s">
         <v>696</v>
       </c>
-      <c r="C699" s="2">
+      <c r="C699">
         <v>0</v>
       </c>
     </row>
@@ -10950,7 +10949,7 @@
       <c r="B700" t="s">
         <v>697</v>
       </c>
-      <c r="C700" s="2">
+      <c r="C700">
         <v>-1</v>
       </c>
     </row>
@@ -10962,7 +10961,7 @@
       <c r="B701" t="s">
         <v>698</v>
       </c>
-      <c r="C701" s="2">
+      <c r="C701">
         <v>-1</v>
       </c>
     </row>
@@ -10974,7 +10973,7 @@
       <c r="B702" t="s">
         <v>699</v>
       </c>
-      <c r="C702" s="2">
+      <c r="C702">
         <v>-1</v>
       </c>
     </row>
@@ -10986,7 +10985,7 @@
       <c r="B703" t="s">
         <v>700</v>
       </c>
-      <c r="C703" s="2">
+      <c r="C703">
         <v>-1</v>
       </c>
     </row>
@@ -10998,7 +10997,7 @@
       <c r="B704" t="s">
         <v>701</v>
       </c>
-      <c r="C704" s="2">
+      <c r="C704">
         <v>0</v>
       </c>
     </row>
@@ -11010,7 +11009,7 @@
       <c r="B705" t="s">
         <v>702</v>
       </c>
-      <c r="C705" s="2">
+      <c r="C705">
         <v>0</v>
       </c>
     </row>
@@ -11022,7 +11021,7 @@
       <c r="B706" t="s">
         <v>703</v>
       </c>
-      <c r="C706" s="2">
+      <c r="C706">
         <v>0</v>
       </c>
     </row>
@@ -11034,7 +11033,7 @@
       <c r="B707" t="s">
         <v>704</v>
       </c>
-      <c r="C707" s="2">
+      <c r="C707">
         <v>0</v>
       </c>
     </row>
@@ -11046,7 +11045,7 @@
       <c r="B708" t="s">
         <v>705</v>
       </c>
-      <c r="C708" s="2">
+      <c r="C708">
         <v>0</v>
       </c>
     </row>
@@ -11058,7 +11057,7 @@
       <c r="B709" t="s">
         <v>706</v>
       </c>
-      <c r="C709" s="2">
+      <c r="C709">
         <v>0</v>
       </c>
     </row>
@@ -11070,7 +11069,7 @@
       <c r="B710" t="s">
         <v>707</v>
       </c>
-      <c r="C710" s="2">
+      <c r="C710">
         <v>-1</v>
       </c>
     </row>
@@ -11082,7 +11081,7 @@
       <c r="B711" t="s">
         <v>708</v>
       </c>
-      <c r="C711" s="2">
+      <c r="C711">
         <v>0</v>
       </c>
     </row>
@@ -11094,7 +11093,7 @@
       <c r="B712" t="s">
         <v>709</v>
       </c>
-      <c r="C712" s="2">
+      <c r="C712">
         <v>0</v>
       </c>
     </row>
@@ -11106,7 +11105,7 @@
       <c r="B713" t="s">
         <v>710</v>
       </c>
-      <c r="C713" s="2">
+      <c r="C713">
         <v>0</v>
       </c>
     </row>
@@ -11118,7 +11117,7 @@
       <c r="B714" t="s">
         <v>711</v>
       </c>
-      <c r="C714" s="2">
+      <c r="C714">
         <v>0</v>
       </c>
     </row>
@@ -11130,7 +11129,7 @@
       <c r="B715" t="s">
         <v>712</v>
       </c>
-      <c r="C715" s="2">
+      <c r="C715">
         <v>0</v>
       </c>
     </row>
@@ -11142,7 +11141,7 @@
       <c r="B716" t="s">
         <v>713</v>
       </c>
-      <c r="C716" s="2">
+      <c r="C716">
         <v>0</v>
       </c>
     </row>
@@ -11154,7 +11153,7 @@
       <c r="B717" t="s">
         <v>714</v>
       </c>
-      <c r="C717" s="2">
+      <c r="C717">
         <v>1</v>
       </c>
     </row>
@@ -11166,7 +11165,7 @@
       <c r="B718" t="s">
         <v>714</v>
       </c>
-      <c r="C718" s="2">
+      <c r="C718">
         <v>2</v>
       </c>
     </row>
@@ -11178,7 +11177,7 @@
       <c r="B719" t="s">
         <v>714</v>
       </c>
-      <c r="C719" s="2">
+      <c r="C719">
         <v>-1</v>
       </c>
     </row>
@@ -11190,7 +11189,7 @@
       <c r="B720" t="s">
         <v>714</v>
       </c>
-      <c r="C720" s="2">
+      <c r="C720">
         <v>0</v>
       </c>
     </row>
@@ -11202,7 +11201,7 @@
       <c r="B721" t="s">
         <v>715</v>
       </c>
-      <c r="C721" s="2">
+      <c r="C721">
         <v>0</v>
       </c>
     </row>
@@ -11214,7 +11213,7 @@
       <c r="B722" t="s">
         <v>716</v>
       </c>
-      <c r="C722" s="2">
+      <c r="C722">
         <v>0</v>
       </c>
     </row>
